--- a/data/face-common-vars.xlsx
+++ b/data/face-common-vars.xlsx
@@ -1710,7 +1710,7 @@
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>READY — Comparable construct in all 3 cohorts and data present in all 3 CSVs</t>
+          <t>NOT USABLE — birthdate (PII), redundant with the independent age column; date-&gt;1e18 numeric-coercion artifact</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="L38" s="18" t="inlineStr">
         <is>
-          <t>PARTIAL — Comparable in 2 of 3 cohorts (Tier B); usable for 2-cohort joint clustering</t>
+          <t>NOT USABLE — 2-cohort (BP/DR), not collected at BP yearly visits</t>
         </is>
       </c>
       <c r="M38" s="17" t="inlineStr">
@@ -8138,8 +8138,12 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="G100" s="98" t="n"/>
-      <c r="H100" s="125" t="n"/>
+      <c r="G100" s="98" t="n">
+        <v>20</v>
+      </c>
+      <c r="H100" s="125" t="n">
+        <v>60</v>
+      </c>
       <c r="I100" s="45" t="inlineStr">
         <is>
           <t>Hematocrit : complements hemoglobin to characterise anemia type (microcytic, macrocytic) and detect dehydration.</t>
@@ -8152,7 +8156,7 @@
       </c>
       <c r="K100" s="45" t="inlineStr">
         <is>
-          <t>[see Codage]</t>
+          <t>% (HCT; L/L entries x100 by rule; sentinels nulled)</t>
         </is>
       </c>
       <c r="L100" s="46" t="inlineStr">
@@ -8738,8 +8742,12 @@
           <t>NUM</t>
         </is>
       </c>
-      <c r="G108" s="98" t="n"/>
-      <c r="H108" s="125" t="n"/>
+      <c r="G108" s="98" t="n">
+        <v>25</v>
+      </c>
+      <c r="H108" s="125" t="n">
+        <v>45</v>
+      </c>
       <c r="I108" s="45" t="inlineStr">
         <is>
           <t>Mean corpuscular hemoglobin concentration : completes erythrocyte indices for differential anemia diagnosis.</t>
@@ -8752,7 +8760,7 @@
       </c>
       <c r="K108" s="45" t="inlineStr">
         <is>
-          <t>g/L or mg/dL (see Codage)</t>
+          <t>g/dL (MCHC; g/L entries /10 by rule)</t>
         </is>
       </c>
       <c r="L108" s="46" t="inlineStr">
@@ -8909,7 +8917,7 @@
       </c>
       <c r="L110" s="46" t="inlineStr">
         <is>
-          <t>PARTIAL — Comparable in 2 of 3 cohorts (Tier B); usable for 2-cohort joint clustering</t>
+          <t>NOT USABLE — beta-hCG pregnancy test — ~0 in non-pregnant (near-zero variance) + 333000 sentinel; not a phenotype</t>
         </is>
       </c>
       <c r="M110" s="47" t="inlineStr">
@@ -9135,7 +9143,7 @@
       </c>
       <c r="L113" s="46" t="inlineStr">
         <is>
-          <t>PARTIAL — Comparable in 2 of 3 cohorts (Tier B); usable for 2-cohort joint clustering</t>
+          <t>NOT USABLE — clozapine dose — SZ-specific treatment marker (SZ median 419mg vs BP n=59 median 3), not a trans-diagnostic phenotype; cohort-incomparable</t>
         </is>
       </c>
       <c r="M113" s="45" t="inlineStr">
@@ -10887,7 +10895,7 @@
       </c>
       <c r="L137" s="23" t="inlineStr">
         <is>
-          <t>PARTIAL — Comparable in 2 of 3 cohorts (Tier B), both with data in CSV</t>
+          <t>NOT USABLE — BP n=79, DR n=0, SZ absent — effectively empty</t>
         </is>
       </c>
       <c r="M137" s="20" t="inlineStr">
@@ -13916,7 +13924,7 @@
       </c>
       <c r="L178" s="5" t="inlineStr">
         <is>
-          <t>READY — Comparable construct in all 3 cohorts and data present in all 3 CSVs</t>
+          <t>NOT USABLE — near-zero-variance medical-history flag (minority &lt;5%); no modelling signal</t>
         </is>
       </c>
       <c r="M178" s="2" t="inlineStr">
@@ -14120,7 +14128,7 @@
       </c>
       <c r="L181" s="5" t="inlineStr">
         <is>
-          <t>READY — Comparable construct in all 3 cohorts and data present in all 3 CSVs</t>
+          <t>NOT USABLE — near-zero-variance medical-history flag (minority &lt;5%); no modelling signal</t>
         </is>
       </c>
       <c r="M181" s="2" t="inlineStr">
@@ -14324,7 +14332,7 @@
       </c>
       <c r="L184" s="5" t="inlineStr">
         <is>
-          <t>READY — Comparable construct in all 3 cohorts and data present in all 3 CSVs</t>
+          <t>NOT USABLE — near-zero-variance medical-history flag (minority &lt;5%); no modelling signal</t>
         </is>
       </c>
       <c r="M184" s="2" t="inlineStr">
@@ -14392,7 +14400,7 @@
       </c>
       <c r="L185" s="5" t="inlineStr">
         <is>
-          <t>READY — Comparable construct in all 3 cohorts and data present in all 3 CSVs</t>
+          <t>NOT USABLE — near-zero-variance medical-history flag (minority &lt;5%); no modelling signal</t>
         </is>
       </c>
       <c r="M185" s="2" t="inlineStr">
@@ -14460,7 +14468,7 @@
       </c>
       <c r="L186" s="5" t="inlineStr">
         <is>
-          <t>READY — Comparable construct in all 3 cohorts and data present in all 3 CSVs</t>
+          <t>NOT USABLE — near-zero-variance medical-history flag (minority &lt;5%); no modelling signal</t>
         </is>
       </c>
       <c r="M186" s="2" t="inlineStr">
@@ -15072,7 +15080,7 @@
       </c>
       <c r="L195" s="5" t="inlineStr">
         <is>
-          <t>READY — Comparable construct in all 3 cohorts and data present in all 3 CSVs</t>
+          <t>NOT USABLE — near-zero-variance medical-history flag (minority &lt;5%); no modelling signal</t>
         </is>
       </c>
       <c r="M195" s="2" t="inlineStr">
@@ -15140,7 +15148,7 @@
       </c>
       <c r="L196" s="5" t="inlineStr">
         <is>
-          <t>READY — Comparable construct in all 3 cohorts and data present in all 3 CSVs</t>
+          <t>NOT USABLE — near-zero-variance medical-history flag (minority &lt;5%); no modelling signal</t>
         </is>
       </c>
       <c r="M196" s="2" t="inlineStr">
@@ -15208,7 +15216,7 @@
       </c>
       <c r="L197" s="5" t="inlineStr">
         <is>
-          <t>READY — Comparable construct in all 3 cohorts and data present in all 3 CSVs</t>
+          <t>NOT USABLE — near-zero-variance medical-history flag (minority &lt;5%); no modelling signal</t>
         </is>
       </c>
       <c r="M197" s="2" t="inlineStr">
@@ -15276,7 +15284,7 @@
       </c>
       <c r="L198" s="5" t="inlineStr">
         <is>
-          <t>READY — Comparable construct in all 3 cohorts and data present in all 3 CSVs</t>
+          <t>NOT USABLE — near-zero-variance medical-history flag (minority &lt;5%); no modelling signal</t>
         </is>
       </c>
       <c r="M198" s="2" t="inlineStr">
@@ -15344,7 +15352,7 @@
       </c>
       <c r="L199" s="5" t="inlineStr">
         <is>
-          <t>READY — Comparable construct in all 3 cohorts and data present in all 3 CSVs</t>
+          <t>NOT USABLE — near-zero-variance medical-history flag (minority &lt;5%); no modelling signal</t>
         </is>
       </c>
       <c r="M199" s="2" t="inlineStr">
@@ -15412,7 +15420,7 @@
       </c>
       <c r="L200" s="5" t="inlineStr">
         <is>
-          <t>READY — Comparable construct in all 3 cohorts and data present in all 3 CSVs</t>
+          <t>NOT USABLE — near-zero-variance medical-history flag (minority &lt;5%); no modelling signal</t>
         </is>
       </c>
       <c r="M200" s="2" t="inlineStr">
@@ -15480,7 +15488,7 @@
       </c>
       <c r="L201" s="5" t="inlineStr">
         <is>
-          <t>READY — Comparable construct in all 3 cohorts and data present in all 3 CSVs</t>
+          <t>NOT USABLE — near-zero-variance medical-history flag (minority &lt;5%); no modelling signal</t>
         </is>
       </c>
       <c r="M201" s="2" t="inlineStr">

--- a/data/face-common-vars.xlsx
+++ b/data/face-common-vars.xlsx
@@ -1208,7 +1208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P218"/>
+  <dimension ref="A1:P224"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="24.1640625" customWidth="1" min="1" max="1"/>
@@ -10314,7 +10314,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>Recode all to {1=Oui, 0=Non, NA=missing}. BP/SZ: 'Oui'→1, 'Non'→0. DR: already numeric, no change needed.</t>
+          <t>Recode all to {1=Oui, 0=Non, NA=missing}. BP/SZ: 'Oui'→1, 'Non'→0. DR: already numeric, no change needed. | SKIP-LOGIC GATE (skip_logic.py): isf05=No drives structural-zero decode of isf07/isf08/isf09.</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
@@ -10392,7 +10392,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>Recode all to {1=Oui, 0=Non, NA=missing}. BP/SZ: 'Oui'→1, 'Non'→0. DR: already numeric, no change needed.</t>
+          <t>Recode all to {1=Oui, 0=Non, NA=missing}. BP/SZ: 'Oui'→1, 'Non'→0. DR: already numeric, no change needed. | SKIP-LOGIC decode: where isf05=No &amp; missing -&gt; 0 (no lifetime attempt = 0 attempts); recovers coverage 38/27/25% -&gt; 89/92/72% (BP/SZ/DR). '&gt;10' ceiling token -&gt; 10 via rules._isf07. Fills only missing cells; existing values kept.</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>Map BP/SZ text → numeric: {'La semaine dernière'→0, 'Il y a entre une semaine et la dernière visite'→0 (collapse to la semaine dernière, OR keep as 0.5 if you want to preserve granularity for BP/SZ-only sub-analyses), 'Il y a entre deux semaines et douze mois'→1, 'Il y a plus d''un an'→2}. DR is already 0/1/2 — no change. Document the BP/SZ 4-to-3 collapse choice.</t>
+          <t>Map BP/SZ text → numeric: {'La semaine dernière'→0, 'Il y a entre une semaine et la dernière visite'→0 (collapse to la semaine dernière, OR keep as 0.5 if you want to preserve granularity for BP/SZ-only sub-analyses), 'Il y a entre deux semaines et douze mois'→1, 'Il y a plus d''un an'→2}. DR is already 0/1/2 — no change. Document the BP/SZ 4-to-3 collapse choice. | SKIP-LOGIC decode: isf05=No &amp; missing -&gt; 0 (no attempt = no violent); cascades into isf08a.</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
@@ -10544,7 +10544,7 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>Recode all to {1=Oui, 0=Non, NA=missing}. BP/SZ: 'Oui'→1, 'Non'→0. DR: already numeric, no change needed.</t>
+          <t>Recode all to {1=Oui, 0=Non, NA=missing}. BP/SZ: 'Oui'→1, 'Non'→0. DR: already numeric, no change needed. | SKIP-LOGIC decode: isf05=No OR isf08=No (&amp; missing) -&gt; 0; recovers coverage 7/7/4% -&gt; 89/92/72% (BP/SZ/DR).</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -10618,7 +10618,7 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>Map BP/SZ text → numeric: {'La semaine dernière'→0, 'Il y a entre une semaine et la dernière visite'→0 (collapse to la semaine dernière, OR keep as 0.5 if you want to preserve granularity for BP/SZ-only sub-analyses), 'Il y a entre deux semaines et douze mois'→1, 'Il y a plus d''un an'→2}. DR is already 0/1/2 — no change. Document the BP/SZ 4-to-3 collapse choice.</t>
+          <t>Map BP/SZ text → numeric: {'La semaine dernière'→0, 'Il y a entre une semaine et la dernière visite'→0 (collapse to la semaine dernière, OR keep as 0.5 if you want to preserve granularity for BP/SZ-only sub-analyses), 'Il y a entre deux semaines et douze mois'→1, 'Il y a plus d''un an'→2}. DR is already 0/1/2 — no change. Document the BP/SZ 4-to-3 collapse choice. | SKIP-LOGIC decode: isf05=No &amp; missing -&gt; 0 (no attempt = no serious); cascades into isf09a.</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -10696,7 +10696,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>Recode all to {1=Oui, 0=Non, NA=missing}. BP/SZ: 'Oui'→1, 'Non'→0. DR: already numeric, no change needed.</t>
+          <t>Recode all to {1=Oui, 0=Non, NA=missing}. BP/SZ: 'Oui'→1, 'Non'→0. DR: already numeric, no change needed. | SKIP-LOGIC decode: isf05=No OR isf09=No (&amp; missing) -&gt; 0; recovers coverage 10/6/9% -&gt; 89/91/72% (BP/SZ/DR). Count parsed via rules._isf09a.</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -16766,6 +16766,454 @@
       <c r="O218" t="inlineStr">
         <is>
           <t>Index score (100+/-15); present in all 3 cohorts</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>NEUROPSYCHOLOGIE</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>cvlt06_</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>cvlt06_</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>CVLT Total Recall, trials 1–5 (verbal learning / acquisition)</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Numérique (somme des rappels libres, essais 1–5)</t>
+        </is>
+      </c>
+      <c r="G219" t="n">
+        <v>0</v>
+      </c>
+      <c r="H219" t="n">
+        <v>80</v>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>FEATURE (verbal episodic memory; BP + SZ only — DR has no CVLT). California Verbal Learning Test total free recall summed over the five learning trials — the canonical measure of verbal learning/acquisition. Adds the verbal episodic-memory domain that is otherwise ABSENT from the 3-cohort battery (processing speed, working memory, verbal reasoning, executive shifting — but no memory). Raw count on an identical 16-word/5-trial CVLT in both cohorts (0–80); SZ sits below BP (median 47 vs 58) = a real memory deficit, not a scale difference. Usable in masked FA as a 2-cohort verbal-memory feature.</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>words recalled (0–80)</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>PARTIAL — Comparable in 2 of 3 cohorts (Tier B); usable for 2-cohort joint clustering</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>cvlt_total_recall</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>2 (BP/SZ)</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>Raw count, same code cvlt06_ in BP &amp; SZ; cap [0,80]; robust-z in-pipeline (do NOT use vendor z cvlt06z_ — sparse/outlier-prone in SZ). DR absent (no verbal-list-learning test). Exclude CVLT recognition (cvlt16/cvlt18 — out-of-range/contaminated).</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>Same code &amp; identical 0–80 scale verified in both cohorts; r=0.82 with delayed recall (distinct construct). BP/SZ only — DR has no CVLT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>NEUROPSYCHOLOGIE</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>cvlt08_</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>avl01103_</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>CVLT Short-delay free recall</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Numérique (rappel libre à court terme)</t>
+        </is>
+      </c>
+      <c r="G220" t="n">
+        <v>0</v>
+      </c>
+      <c r="H220" t="n">
+        <v>16</v>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>FEATURE (verbal episodic memory; BP + SZ only — DR has no CVLT). Free recall of the 16-word list after a short delay + interference list — verbal retention across a brief delay. Component of the CVLT verbal-memory domain. Identical 0–16 scale in both cohorts. Near-duplicate of long-delay free recall (r=0.89), so best combined with the other recall indices into a single masked verbal-memory domain rather than entered as an independent feature.</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>words recalled (0–16)</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>PARTIAL — Comparable in 2 of 3 cohorts (Tier B); usable for 2-cohort joint clustering</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>cvlt_short_delay_free_recall</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>2 (BP/SZ)</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>Raw count; cap [0,16]; BP cvlt08_ ↔ SZ avl01103_ (codes differ, same construct &amp; scale — verified); robust-z in-pipeline. r=0.89 with long-delay → composite into one verbal-memory domain to avoid double-counting. DR absent.</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>BP cvlt08_ ↔ SZ avl01103_; both 0–16 (BP median 12 vs SZ 9); r=0.89 with long-delay (near-duplicate). DR has no CVLT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>NEUROPSYCHOLOGIE</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>cvlt10_</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>avl01135_</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>CVLT Long-delay free recall (delayed retention)</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Numérique (rappel libre à long terme)</t>
+        </is>
+      </c>
+      <c r="G221" t="n">
+        <v>0</v>
+      </c>
+      <c r="H221" t="n">
+        <v>16</v>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>FEATURE (verbal episodic memory; BP + SZ only — DR has no CVLT). Free recall of the 16-word list after a ~20-minute delay — delayed retention / consolidation, the standard CVLT "delayed recall" score and clinically dissociable from acquisition (r=0.82 with total recall). Component of the CVLT verbal-memory domain. Identical 0–16 scale in both cohorts; SZ below BP (median 10 vs 13) = real deficit.</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>words recalled (0–16)</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>PARTIAL — Comparable in 2 of 3 cohorts (Tier B); usable for 2-cohort joint clustering</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>cvlt_long_delay_free_recall</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>2 (BP/SZ)</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>Raw count; cap [0,16]; BP cvlt10_ ↔ SZ avl01135_ (codes differ, same construct &amp; scale — verified); robust-z in-pipeline. DR absent.</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>BP cvlt10_ ↔ SZ avl01135_; both 0–16 (BP median 13 vs SZ 10). DR has no CVLT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>NEUROPSYCHOLOGIE</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>fv01_</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>fv01_</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>fv05</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Verbal fluency — phonemic (letter): total correct words</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Numérique (nombre de mots corrects en 60 s)</t>
+        </is>
+      </c>
+      <c r="G222" t="n">
+        <v>0</v>
+      </c>
+      <c r="H222" t="n">
+        <v>60</v>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>FEATURE — phonemic/letter verbal fluency (correct words in 60 s for a given letter). Taps executive function: strategic retrieval, self-monitoring, set-shifting/flexibility; a robust trans-diagnostic cognitive marker present in all 3 cohorts. Raw word count on the same scale (BP/SZ letter "P"; DR "phonologie"); SZ/DR below BP = real cognitive deficit. Complements TMT B−A as an executive/flexibility indicator (dim: Cognitive Flexibility).</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>words / 60 s (0–60)</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>READY — Comparable in 3 cohorts (Tier A)</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>verbal_fluency_phonemic</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>3 (BP/SZ/DR)</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>Raw word count; cap [0,60] (BP has a 229 data-entry outlier); robust-z in-pipeline. COLUMN MAP DIFFERS: BP/SZ `fv01_` but DR=`fv05` (DR `fv01` = "choix du questionnaire", NOT a score). Exclude SZ `FV3_*` (separate computerized TAP flexibility test). Added 2026-06-03 review (not in original neuropsy_features.yaml).</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>BP/SZ `fv01_` (letter P) ↔ DR `fv05` (phonologie); raw counts, medians 24/18/20 — same scale verified; SZ&lt;BP real deficit. Coverage 67/42/55%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>NEUROPSYCHOLOGIE</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>fv12_</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>fv12_</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>fv02</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Verbal fluency — semantic (category): total correct words</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Numérique (nombre de mots corrects en 60 s)</t>
+        </is>
+      </c>
+      <c r="G223" t="n">
+        <v>0</v>
+      </c>
+      <c r="H223" t="n">
+        <v>80</v>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>FEATURE — semantic/category verbal fluency (correct words in 60 s for a category). Taps semantic-memory access plus executive search; a standard trans-diagnostic cognitive marker in all 3 cohorts. Raw word count, same scale; SZ/DR below BP = real deficit. Complements phonemic fluency (semantic store vs strategic search) for the Cognitive Flexibility dimension.</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>words / 60 s (0–80)</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>READY — Comparable in 3 cohorts (Tier A)</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>verbal_fluency_semantic</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>3 (BP/SZ/DR)</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>Raw word count; cap [0,80]; robust-z in-pipeline. COLUMN MAP DIFFERS: BP/SZ `fv12_` but DR=`fv02`. Category: BP/SZ "animaux"; DR "animaux OU fruits" (patient choice — minor comparability caveat). Added 2026-06-03 review.</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>BP/SZ `fv12_` (animals) ↔ DR `fv02` (animals or fruits); raw counts, medians 32/24/26 — same scale verified; SZ&lt;BP real deficit. Coverage 67/42/55%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>AUTO-QUESTIONNAIRES</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>qidsr113</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>qids13</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>QIDS-SR16 item 13 — general interest (anhedonia)</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Likert 0–3 (0 = intérêt normal … 3 = perte quasi totale d'intérêt)</t>
+        </is>
+      </c>
+      <c r="G224" t="n">
+        <v>0</v>
+      </c>
+      <c r="H224" t="n">
+        <v>3</v>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>FEATURE (Anhedonia; BP + DR only — SZ has NO QIDS). QIDS-SR16 item 13 ("enthousiasme / intérêt général") is a direct self-report anhedonia indicator (loss of interest). The Anhedonia target dimension is otherwise nearly unmeasured (SHAPS is DR-only). Single item → thin indicator; best composited with other interest/pleasure items into an anhedonia domain. SZ has no anhedonia self-report, so this dimension is 2-cohort (BP/DR).</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Likert 0–3</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>PARTIAL — Comparable in 2 of 3 cohorts (Tier B); usable for 2-cohort joint clustering</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>qids_anhedonia_interest</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>2 (BP/DR)</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>0–3 Likert, identical item in BP `qidsr113` &amp; DR `qids13`; SZ absent (no QIDS). Single-item anhedonia proxy — consider compositing with SHAPS (DR) / MADRS "inability to feel" item for a fuller domain. Do NOT duplicate other QIDS items (sleep→PSQI, suicide→ISF, severity→MADRS).</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>BP `qidsr113` == DR `qids13` (identical item, 0–3); ~90% coverage. SZ has no QIDS → no SZ anhedonia measure (dim 4 = Anhedonia is BP/DR only).</t>
         </is>
       </c>
     </row>

--- a/data/face-common-vars.xlsx
+++ b/data/face-common-vars.xlsx
@@ -1208,7 +1208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P224"/>
+  <dimension ref="A1:P226"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="24.1640625" customWidth="1" min="1" max="1"/>
@@ -12806,158 +12806,150 @@
       </c>
     </row>
     <row r="164" ht="21" customFormat="1" customHeight="1" s="13">
-      <c r="A164" s="11" t="inlineStr">
-        <is>
-          <t>NEUROPSYCHOLOGIE</t>
-        </is>
-      </c>
-      <c r="B164" s="11" t="inlineStr">
-        <is>
-          <t>cclin01_</t>
-        </is>
-      </c>
-      <c r="C164" s="11" t="inlineStr">
-        <is>
-          <t>cclin01_</t>
-        </is>
-      </c>
-      <c r="D164" s="92" t="inlineStr">
-        <is>
-          <t>cclin01</t>
-        </is>
-      </c>
-      <c r="E164" s="11" t="inlineStr">
-        <is>
-          <t>Âge du patient (au moment de l'évaluation cognitive)</t>
-        </is>
-      </c>
-      <c r="F164" s="11" t="inlineStr">
-        <is>
-          <t>Numérique (années)</t>
-        </is>
-      </c>
-      <c r="G164" s="92" t="n">
-        <v>16</v>
-      </c>
-      <c r="H164" s="119" t="n">
-        <v>90</v>
-      </c>
-      <c r="I164" s="11" t="inlineStr">
-        <is>
-          <t>COVARIATE (not a feature). Age at testing is the single largest determinant of neuropsychological performance, and raw timed scores (TMT) are strongly age-dependent. The cohorts differ markedly in age (DR median 52 vs BP 39 vs SZ 32), so age is retained to residualize the cognitive features and prevent cohort age imbalance from masquerading as a trans-diagnostic cognitive difference.</t>
-        </is>
-      </c>
-      <c r="J164" s="11" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="K164" s="11" t="inlineStr">
-        <is>
-          <t>free text (NLP required)</t>
-        </is>
-      </c>
-      <c r="L164" s="12" t="inlineStr">
-        <is>
-          <t>NOT USABLE — redundant with demographic age; cognition residualizes on age+sex+education_years</t>
-        </is>
-      </c>
-      <c r="M164" s="11" t="inlineStr">
-        <is>
-          <t>cclin01</t>
+      <c r="A164" s="65" t="inlineStr">
+        <is>
+          <t>SUBSTANCES</t>
+        </is>
+      </c>
+      <c r="B164" s="66" t="inlineStr">
+        <is>
+          <t>suoccur_alcool</t>
+        </is>
+      </c>
+      <c r="C164" s="66" t="inlineStr">
+        <is>
+          <t>suoccur_alcool</t>
+        </is>
+      </c>
+      <c r="D164" s="103" t="n"/>
+      <c r="E164" s="66" t="inlineStr">
+        <is>
+          <t>Trouble lié à l'usage d'alcool au cours de la vie (abus ou dépendance, MINI)</t>
+        </is>
+      </c>
+      <c r="F164" s="66" t="inlineStr">
+        <is>
+          <t>BP : 0=Non, 1=Oui ; SZ : Y=Yes, N=No, U=Unknown ; harmonisé → 1=Oui, 0=Non, U→NaN</t>
+        </is>
+      </c>
+      <c r="G164" s="103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" s="132" t="n">
+        <v>1</v>
+      </c>
+      <c r="I164" s="66" t="inlineStr">
+        <is>
+          <t>Lifetime alcohol-use disorder (abuse or dependence) is a major transdiagnostic comorbidity in severe mental illness: it elevates suicide risk, worsens episode frequency, course and treatment response, and adds cognitive, hepatic and metabolic burden in both bipolar disorder and schizophrenia. As a MINI-derived lifetime abuse-or-dependence flag it is a clean addiction/impulsivity marker — a target transdiagnostic dimension otherwise unrepresented in the dictionary. Comparable in BP and SZ; the depression cohort has no equivalent lifetime substance-use-disorder item (its MINI substance module was not extracted to the CSV).</t>
+        </is>
+      </c>
+      <c r="J164" s="66" t="inlineStr">
+        <is>
+          <t>int8 binary</t>
+        </is>
+      </c>
+      <c r="K164" s="66" t="inlineStr">
+        <is>
+          <t>{0=No/Non, 1=Yes/Oui, NA=Unknown}</t>
+        </is>
+      </c>
+      <c r="L164" s="67" t="inlineStr">
+        <is>
+          <t>PARTIAL — Comparable in 2 of 3 cohorts (Tier B); usable for 2-cohort joint clustering</t>
+        </is>
+      </c>
+      <c r="M164" s="66" t="inlineStr">
+        <is>
+          <t>suoccur_alcool</t>
         </is>
       </c>
       <c r="N164" s="22" t="inlineStr">
         <is>
-          <t>3 (BP/SZ/DR)</t>
+          <t>2 (BP/SZ)</t>
         </is>
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>Use as covariate (TMT raw times not age-normed); not a feature. QC [16,90].</t>
+          <t>SZ: map Y→1, N→0, U→NaN (text→code). BP: already 0/1 — QA-check that 0 = true negative vs not-assessed (BP column is fully dense). DR: no comparable lifetime alcohol-use-disorder variable (MINI substance module absent from depression.csv) → DR column left empty.</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>NUM, comparable all 3 cohorts</t>
+          <t>BP &amp; SZ share the identical extraction name (suoccur_alcool) and the same MINI-derived construct: lifetime alcohol abuse-or-dependence ('au cours de la vie'), NOT current (the current-month variant is ABUDEP_alcool). Difference is storage only: BP 0/1 (dense, no missing), SZ Y/N/U.</t>
         </is>
       </c>
     </row>
     <row r="165" ht="21" customFormat="1" customHeight="1" s="60">
-      <c r="A165" s="11" t="inlineStr">
-        <is>
-          <t>NEUROPSYCHOLOGIE</t>
-        </is>
-      </c>
-      <c r="B165" s="11" t="inlineStr">
-        <is>
-          <t>cclin08_</t>
-        </is>
-      </c>
-      <c r="C165" s="11" t="inlineStr">
-        <is>
-          <t>cclin08_</t>
-        </is>
-      </c>
-      <c r="D165" s="92" t="inlineStr">
-        <is>
-          <t>cclin08</t>
-        </is>
-      </c>
-      <c r="E165" s="11" t="inlineStr">
-        <is>
-          <t>Education (years since CP) — cognition covariate</t>
-        </is>
-      </c>
-      <c r="F165" s="11" t="inlineStr">
-        <is>
-          <t>Numérique (années)</t>
-        </is>
-      </c>
-      <c r="G165" s="92" t="n">
+      <c r="A165" s="65" t="inlineStr">
+        <is>
+          <t>SUBSTANCES</t>
+        </is>
+      </c>
+      <c r="B165" s="66" t="inlineStr">
+        <is>
+          <t>suoccur_cannabis</t>
+        </is>
+      </c>
+      <c r="C165" s="66" t="inlineStr">
+        <is>
+          <t>suoccur_cannabis</t>
+        </is>
+      </c>
+      <c r="D165" s="103" t="n"/>
+      <c r="E165" s="66" t="inlineStr">
+        <is>
+          <t>Trouble lié à l'usage de cannabis au cours de la vie (abus ou dépendance, MINI)</t>
+        </is>
+      </c>
+      <c r="F165" s="66" t="inlineStr">
+        <is>
+          <t>BP : 0=Non, 1=Oui ; SZ : Y=Yes, N=No, U=Unknown ; harmonisé → 1=Oui, 0=Non, U→NaN</t>
+        </is>
+      </c>
+      <c r="G165" s="103" t="n">
         <v>0</v>
       </c>
-      <c r="H165" s="119" t="n">
-        <v>30</v>
-      </c>
-      <c r="I165" s="11" t="inlineStr">
-        <is>
-          <t>COVARIATE (not a feature). Years of education indexes premorbid cognitive reserve — a major, non-illness source of variance in every cognitive test and a classic confounder of patient-group comparisons. Retained to separate illness-related cognitive variation from educational attainment (SZ records grade level = years since CP, comparable to BP/DR years).</t>
-        </is>
-      </c>
-      <c r="J165" s="11" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="K165" s="11" t="inlineStr">
-        <is>
-          <t>years of schooling since CP</t>
-        </is>
-      </c>
-      <c r="L165" s="12" t="inlineStr">
-        <is>
-          <t>READY — covariate (cognitive reserve); residualize_on, NOT a phenotype feature; neuropsy_features.yaml</t>
-        </is>
-      </c>
-      <c r="M165" s="11" t="inlineStr">
-        <is>
-          <t>education_years</t>
+      <c r="H165" s="132" t="n">
+        <v>1</v>
+      </c>
+      <c r="I165" s="66" t="inlineStr">
+        <is>
+          <t>Lifetime cannabis-use disorder (abuse or dependence) is a key transdiagnostic comorbidity, robustly linked to earlier illness onset, psychotic symptomatology, poorer outcome and higher relapse risk in both bipolar disorder and schizophrenia, and is the most prevalent illicit-substance disorder in these cohorts. MINI-derived lifetime abuse-or-dependence flag, comparable in BP and SZ. The depression cohort has only a cannabis *consumption* item (suoccur_cannabis_lt = DCCAN), a different construct, so DR is left out to preserve comparability.</t>
+        </is>
+      </c>
+      <c r="J165" s="66" t="inlineStr">
+        <is>
+          <t>int8 binary</t>
+        </is>
+      </c>
+      <c r="K165" s="66" t="inlineStr">
+        <is>
+          <t>{0=No/Non, 1=Yes/Oui, NA=Unknown}</t>
+        </is>
+      </c>
+      <c r="L165" s="67" t="inlineStr">
+        <is>
+          <t>PARTIAL — Comparable in 2 of 3 cohorts (Tier B); usable for 2-cohort joint clustering</t>
+        </is>
+      </c>
+      <c r="M165" s="66" t="inlineStr">
+        <is>
+          <t>suoccur_cannabis</t>
         </is>
       </c>
       <c r="N165" s="22" t="inlineStr">
         <is>
-          <t>3 (BP/SZ/DR)</t>
+          <t>2 (BP/SZ)</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>Covariate for cognition (residualize), not a phenotype feature</t>
+          <t>SZ: map Y→1, N→0, U→NaN (text→code). BP: already 0/1. DR: only a consumption question (suoccur_cannabis_lt = DCCAN, 'Consommez-vous du cannabis?', ~26% coverage) — a use *level*, not a use disorder, so not comparable → DR column left empty.</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Comparable all 3; SZ coded grade-level = years since CP</t>
+          <t>BP &amp; SZ share the identical extraction name (suoccur_cannabis) and the same MINI lifetime abuse-or-dependence construct; storage differs only (BP 0/1 vs SZ Y/N/U). DR's suoccur_cannabis_lt measures consumption, not disorder → excluded.</t>
         </is>
       </c>
     </row>
@@ -12969,58 +12961,58 @@
       </c>
       <c r="B166" s="11" t="inlineStr">
         <is>
-          <t>tmta01_</t>
+          <t>cclin01_</t>
         </is>
       </c>
       <c r="C166" s="11" t="inlineStr">
         <is>
-          <t>tmt0101_</t>
+          <t>cclin01_</t>
         </is>
       </c>
       <c r="D166" s="92" t="inlineStr">
         <is>
-          <t>tmta01</t>
+          <t>cclin01</t>
         </is>
       </c>
       <c r="E166" s="11" t="inlineStr">
         <is>
-          <t>Trail Making Test A time (psychomotor speed)</t>
+          <t>Âge du patient (au moment de l'évaluation cognitive)</t>
         </is>
       </c>
       <c r="F166" s="11" t="inlineStr">
         <is>
-          <t>Numérique (s) ; codes diffèrent (SZ TMT0101 vs BP/DR TMTA01)</t>
+          <t>Numérique (années)</t>
         </is>
       </c>
       <c r="G166" s="92" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="H166" s="119" t="n">
-        <v>400</v>
+        <v>90</v>
       </c>
       <c r="I166" s="11" t="inlineStr">
         <is>
-          <t>FEATURE — psychomotor processing speed and visual scanning/attention (Trail Making Test, Part A: connect numbers 1-2-3… in order). Provides the basic-speed baseline against which the executive Part B is interpreted. Processing speed is among the most reproducibly impaired domains across mood and psychotic disorders, making it a strong trans-diagnostic marker. Raw time in seconds, identical scale in all three cohorts.</t>
+          <t>COVARIATE (not a feature). Age at testing is the single largest determinant of neuropsychological performance, and raw timed scores (TMT) are strongly age-dependent. The cohorts differ markedly in age (DR median 52 vs BP 39 vs SZ 32), so age is retained to residualize the cognitive features and prevent cohort age imbalance from masquerading as a trans-diagnostic cognitive difference.</t>
         </is>
       </c>
       <c r="J166" s="11" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="K166" s="11" t="inlineStr">
         <is>
-          <t>seconds</t>
+          <t>free text (NLP required)</t>
         </is>
       </c>
       <c r="L166" s="12" t="inlineStr">
         <is>
-          <t>READY — Comparable in 3 cohorts (Tier A); neuropsy_features.yaml 2026-05-30</t>
-        </is>
-      </c>
-      <c r="M166" s="15" t="inlineStr">
-        <is>
-          <t>tmt_a_time_sec</t>
+          <t>NOT USABLE — redundant with demographic age; cognition residualizes on age+sex+education_years</t>
+        </is>
+      </c>
+      <c r="M166" s="11" t="inlineStr">
+        <is>
+          <t>cclin01</t>
         </is>
       </c>
       <c r="N166" s="22" t="inlineStr">
@@ -13030,12 +13022,12 @@
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>Time in seconds (numeric, NOT free text); sentinels nulled by bound</t>
+          <t>Use as covariate (TMT raw times not age-normed); not a feature. QC [16,90].</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Raw seconds, same scale all 3 cohorts</t>
+          <t>NUM, comparable all 3 cohorts</t>
         </is>
       </c>
     </row>
@@ -13047,38 +13039,38 @@
       </c>
       <c r="B167" s="11" t="inlineStr">
         <is>
-          <t>tmtb01_</t>
+          <t>cclin08_</t>
         </is>
       </c>
       <c r="C167" s="11" t="inlineStr">
         <is>
-          <t>tmt0102_</t>
+          <t>cclin08_</t>
         </is>
       </c>
       <c r="D167" s="92" t="inlineStr">
         <is>
-          <t>tmtb01</t>
+          <t>cclin08</t>
         </is>
       </c>
       <c r="E167" s="11" t="inlineStr">
         <is>
-          <t>Trail Making Test B time (executive / set-shifting)</t>
+          <t>Education (years since CP) — cognition covariate</t>
         </is>
       </c>
       <c r="F167" s="11" t="inlineStr">
         <is>
-          <t>Numérique (s)</t>
+          <t>Numérique (années)</t>
         </is>
       </c>
       <c r="G167" s="92" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H167" s="119" t="n">
-        <v>600</v>
+        <v>30</v>
       </c>
       <c r="I167" s="11" t="inlineStr">
         <is>
-          <t>FEATURE — executive function: set-shifting / cognitive flexibility (Trail Making Test, Part B: alternate numbers and letters 1-A-2-B…). Adds a task-switching demand on top of Part A's speed; a canonical, widely used index of mental flexibility that is sensitive across BP, SZ and DR. Raw time in seconds, same scale all three cohorts.</t>
+          <t>COVARIATE (not a feature). Years of education indexes premorbid cognitive reserve — a major, non-illness source of variance in every cognitive test and a classic confounder of patient-group comparisons. Retained to separate illness-related cognitive variation from educational attainment (SZ records grade level = years since CP, comparable to BP/DR years).</t>
         </is>
       </c>
       <c r="J167" s="11" t="inlineStr">
@@ -13088,17 +13080,17 @@
       </c>
       <c r="K167" s="11" t="inlineStr">
         <is>
-          <t>seconds</t>
+          <t>years of schooling since CP</t>
         </is>
       </c>
       <c r="L167" s="12" t="inlineStr">
         <is>
-          <t>READY — Comparable in 3 cohorts (Tier A); neuropsy_features.yaml 2026-05-30</t>
-        </is>
-      </c>
-      <c r="M167" s="15" t="inlineStr">
-        <is>
-          <t>tmt_b_time_sec</t>
+          <t>READY — covariate (cognitive reserve); residualize_on, NOT a phenotype feature; neuropsy_features.yaml</t>
+        </is>
+      </c>
+      <c r="M167" s="11" t="inlineStr">
+        <is>
+          <t>education_years</t>
         </is>
       </c>
       <c r="N167" s="22" t="inlineStr">
@@ -13108,12 +13100,12 @@
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>Time in seconds (numeric); sentinels 999/1817 nulled by bound</t>
+          <t>Covariate for cognition (residualize), not a phenotype feature</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Raw seconds, all 3 cohorts</t>
+          <t>Comparable all 3; SZ coded grade-level = years since CP</t>
         </is>
       </c>
     </row>
@@ -13125,38 +13117,38 @@
       </c>
       <c r="B168" s="11" t="inlineStr">
         <is>
-          <t>tmtba01_</t>
+          <t>tmta01_</t>
         </is>
       </c>
       <c r="C168" s="11" t="inlineStr">
         <is>
-          <t>tmtba01_</t>
+          <t>tmt0101_</t>
         </is>
       </c>
       <c r="D168" s="92" t="inlineStr">
         <is>
-          <t>tmtba01</t>
+          <t>tmta01</t>
         </is>
       </c>
       <c r="E168" s="11" t="inlineStr">
         <is>
-          <t>TMT B−A — Différence de temps (interférence)</t>
+          <t>Trail Making Test A time (psychomotor speed)</t>
         </is>
       </c>
       <c r="F168" s="11" t="inlineStr">
         <is>
-          <t>Numérique (s)</t>
+          <t>Numérique (s) ; codes diffèrent (SZ TMT0101 vs BP/DR TMTA01)</t>
         </is>
       </c>
       <c r="G168" s="92" t="n">
-        <v>-100</v>
+        <v>5</v>
       </c>
       <c r="H168" s="119" t="n">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="I168" s="11" t="inlineStr">
         <is>
-          <t>FEATURE — purified executive interference / set-shifting cost. The B−A time difference subtracts basic processing and motor speed (Part A) from Part B, isolating the cognitive-flexibility component and reducing the influence of peripheral slowing. A cleaner executive contrast than B alone; same raw-seconds scale across cohorts.</t>
+          <t>FEATURE — psychomotor processing speed and visual scanning/attention (Trail Making Test, Part A: connect numbers 1-2-3… in order). Provides the basic-speed baseline against which the executive Part B is interpreted. Processing speed is among the most reproducibly impaired domains across mood and psychotic disorders, making it a strong trans-diagnostic marker. Raw time in seconds, identical scale in all three cohorts.</t>
         </is>
       </c>
       <c r="J168" s="11" t="inlineStr">
@@ -13166,17 +13158,17 @@
       </c>
       <c r="K168" s="11" t="inlineStr">
         <is>
-          <t>[see Codage]</t>
+          <t>seconds</t>
         </is>
       </c>
       <c r="L168" s="12" t="inlineStr">
         <is>
-          <t>NOT USABLE — sensitivity-only (TMT B-A interference, collinear); excluded from main matrix</t>
-        </is>
-      </c>
-      <c r="M168" s="11" t="inlineStr">
-        <is>
-          <t>tmtba01</t>
+          <t>READY — Comparable in 3 cohorts (Tier A); neuropsy_features.yaml 2026-05-30</t>
+        </is>
+      </c>
+      <c r="M168" s="15" t="inlineStr">
+        <is>
+          <t>tmt_a_time_sec</t>
         </is>
       </c>
       <c r="N168" s="22" t="inlineStr">
@@ -13186,12 +13178,12 @@
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>Feature; sanity [-100,700].</t>
+          <t>Time in seconds (numeric, NOT free text); sentinels nulled by bound</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Raw seconds, all 3 cohorts</t>
+          <t>Raw seconds, same scale all 3 cohorts</t>
         </is>
       </c>
     </row>
@@ -13203,38 +13195,38 @@
       </c>
       <c r="B169" s="11" t="inlineStr">
         <is>
-          <t>similstd_wais4</t>
+          <t>tmtb01_</t>
         </is>
       </c>
       <c r="C169" s="11" t="inlineStr">
         <is>
-          <t>similstd_w</t>
+          <t>tmt0102_</t>
         </is>
       </c>
       <c r="D169" s="92" t="inlineStr">
         <is>
-          <t>similstd</t>
+          <t>tmtb01</t>
         </is>
       </c>
       <c r="E169" s="11" t="inlineStr">
         <is>
-          <t>WAIS Similarities (verbal reasoning), standard score</t>
+          <t>Trail Making Test B time (executive / set-shifting)</t>
         </is>
       </c>
       <c r="F169" s="11" t="inlineStr">
         <is>
-          <t>Numérique (note standard)</t>
+          <t>Numérique (s)</t>
         </is>
       </c>
       <c r="G169" s="92" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H169" s="119" t="n">
-        <v>19</v>
+        <v>600</v>
       </c>
       <c r="I169" s="11" t="inlineStr">
         <is>
-          <t>CORE FEATURE — verbal abstract reasoning / concept formation (WAIS Similarities: explain how two words are alike). A principal Verbal Comprehension subtest and a robust proxy for crystallized verbal intelligence. Available and scaled identically (age-normed scaled score, mean 10 / SD 3) in all three cohorts, so it anchors the trans-diagnostic verbal-reasoning dimension.</t>
+          <t>FEATURE — executive function: set-shifting / cognitive flexibility (Trail Making Test, Part B: alternate numbers and letters 1-A-2-B…). Adds a task-switching demand on top of Part A's speed; a canonical, widely used index of mental flexibility that is sensitive across BP, SZ and DR. Raw time in seconds, same scale all three cohorts.</t>
         </is>
       </c>
       <c r="J169" s="11" t="inlineStr">
@@ -13244,7 +13236,7 @@
       </c>
       <c r="K169" s="11" t="inlineStr">
         <is>
-          <t>WAIS Similarities scaled score (1-19)</t>
+          <t>seconds</t>
         </is>
       </c>
       <c r="L169" s="12" t="inlineStr">
@@ -13252,9 +13244,9 @@
           <t>READY — Comparable in 3 cohorts (Tier A); neuropsy_features.yaml 2026-05-30</t>
         </is>
       </c>
-      <c r="M169" s="11" t="inlineStr">
-        <is>
-          <t>wais_similitudes_std</t>
+      <c r="M169" s="15" t="inlineStr">
+        <is>
+          <t>tmt_b_time_sec</t>
         </is>
       </c>
       <c r="N169" s="22" t="inlineStr">
@@ -13264,12 +13256,12 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>WAIS scaled score (edition-comparable); SZ stray 20 nulled by bound</t>
+          <t>Time in seconds (numeric); sentinels 999/1817 nulled by bound</t>
         </is>
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>WAIS scaled score (mean10/SD3); all 3; WAIS-3/4 both normed</t>
+          <t>Raw seconds, all 3 cohorts</t>
         </is>
       </c>
     </row>
@@ -13281,34 +13273,38 @@
       </c>
       <c r="B170" s="11" t="inlineStr">
         <is>
-          <t>mat_std_w</t>
+          <t>tmtba01_</t>
         </is>
       </c>
       <c r="C170" s="11" t="inlineStr">
         <is>
-          <t>mat_std_w</t>
-        </is>
-      </c>
-      <c r="D170" s="92" t="n"/>
+          <t>tmtba01_</t>
+        </is>
+      </c>
+      <c r="D170" s="92" t="inlineStr">
+        <is>
+          <t>tmtba01</t>
+        </is>
+      </c>
       <c r="E170" s="11" t="inlineStr">
         <is>
-          <t>WAIS-IV Matrices — Note standard</t>
+          <t>TMT B−A — Différence de temps (interférence)</t>
         </is>
       </c>
       <c r="F170" s="11" t="inlineStr">
         <is>
-          <t>Numérique (note standard)</t>
+          <t>Numérique (s)</t>
         </is>
       </c>
       <c r="G170" s="92" t="n">
-        <v>1</v>
+        <v>-100</v>
       </c>
       <c r="H170" s="119" t="n">
-        <v>19</v>
+        <v>700</v>
       </c>
       <c r="I170" s="11" t="inlineStr">
         <is>
-          <t>FEATURE (supplementary; BP + SZ only — DR absent). Nonverbal fluid / perceptual reasoning (WAIS Matrix Reasoning: complete a visual pattern). Core Perceptual Reasoning subtest; complements verbal reasoning with a culture-light fluid-intelligence measure. Age-normed scaled score (mean 10 / SD 3). Usable in masked FA, but its cohort-aligned missingness makes it a sensitivity feature, not part of the all-cohort stratification core.</t>
+          <t>FEATURE — purified executive interference / set-shifting cost. The B−A time difference subtracts basic processing and motor speed (Part A) from Part B, isolating the cognitive-flexibility component and reducing the influence of peripheral slowing. A cleaner executive contrast than B alone; same raw-seconds scale across cohorts.</t>
         </is>
       </c>
       <c r="J170" s="11" t="inlineStr">
@@ -13318,32 +13314,32 @@
       </c>
       <c r="K170" s="11" t="inlineStr">
         <is>
-          <t>mmHg</t>
+          <t>[see Codage]</t>
         </is>
       </c>
       <c r="L170" s="12" t="inlineStr">
         <is>
-          <t>NOT USABLE — 2-cohort sensitivity-only (WAIS matrices); excluded from main 3-cohort matrix per neuropsy_features.yaml</t>
+          <t>NOT USABLE — sensitivity-only (TMT B-A interference, collinear); excluded from main matrix</t>
         </is>
       </c>
       <c r="M170" s="11" t="inlineStr">
         <is>
-          <t>mat_std_w</t>
+          <t>tmtba01</t>
         </is>
       </c>
       <c r="N170" s="22" t="inlineStr">
         <is>
-          <t>2 (BP/SZ)</t>
+          <t>3 (BP/SZ/DR)</t>
         </is>
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>Masked-FA feature; cohort-missing risk for stratification; cap [1,19].</t>
+          <t>Feature; sanity [-100,700].</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Scaled score; BP+SZ only (DR absent)</t>
+          <t>Raw seconds, all 3 cohorts</t>
         </is>
       </c>
     </row>
@@ -13355,22 +13351,22 @@
       </c>
       <c r="B171" s="11" t="inlineStr">
         <is>
-          <t>nstand_w</t>
+          <t>similstd_wais4</t>
         </is>
       </c>
       <c r="C171" s="11" t="inlineStr">
         <is>
-          <t>nstand_w</t>
+          <t>similstd_w</t>
         </is>
       </c>
       <c r="D171" s="92" t="inlineStr">
         <is>
-          <t>nstand</t>
+          <t>similstd</t>
         </is>
       </c>
       <c r="E171" s="11" t="inlineStr">
         <is>
-          <t>WAIS Digit Span (working memory), standard score</t>
+          <t>WAIS Similarities (verbal reasoning), standard score</t>
         </is>
       </c>
       <c r="F171" s="11" t="inlineStr">
@@ -13386,7 +13382,7 @@
       </c>
       <c r="I171" s="11" t="inlineStr">
         <is>
-          <t>CORE FEATURE — auditory-verbal short-term and working memory (WAIS Digit Span: repeat digit sequences forward, backward, and in order). The canonical working-memory subtest and a domain central to trans-diagnostic cognitive impairment. The age-normed scaled score is comparable across all three cohorts; the standard score is used because BP's raw span values are corrupted. Anchors the working-memory dimension.</t>
+          <t>CORE FEATURE — verbal abstract reasoning / concept formation (WAIS Similarities: explain how two words are alike). A principal Verbal Comprehension subtest and a robust proxy for crystallized verbal intelligence. Available and scaled identically (age-normed scaled score, mean 10 / SD 3) in all three cohorts, so it anchors the trans-diagnostic verbal-reasoning dimension.</t>
         </is>
       </c>
       <c r="J171" s="11" t="inlineStr">
@@ -13396,7 +13392,7 @@
       </c>
       <c r="K171" s="11" t="inlineStr">
         <is>
-          <t>WAIS Digit Span scaled score (1-19)</t>
+          <t>WAIS Similarities scaled score (1-19)</t>
         </is>
       </c>
       <c r="L171" s="12" t="inlineStr">
@@ -13406,7 +13402,7 @@
       </c>
       <c r="M171" s="11" t="inlineStr">
         <is>
-          <t>wais_digitspan_std</t>
+          <t>wais_similitudes_std</t>
         </is>
       </c>
       <c r="N171" s="22" t="inlineStr">
@@ -13416,12 +13412,12 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>Standard score only (BP raw nbrut_w corrupted)</t>
+          <t>WAIS scaled score (edition-comparable); SZ stray 20 nulled by bound</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Scaled score all 3; BP raw corrupted but standard score clean</t>
+          <t>WAIS scaled score (mean10/SD3); all 3; WAIS-3/4 both normed</t>
         </is>
       </c>
     </row>
@@ -13431,25 +13427,25 @@
           <t>NEUROPSYCHOLOGIE</t>
         </is>
       </c>
-      <c r="B172" s="11" t="n"/>
+      <c r="B172" s="11" t="inlineStr">
+        <is>
+          <t>mat_std_w</t>
+        </is>
+      </c>
       <c r="C172" s="11" t="inlineStr">
         <is>
-          <t>arithstd_w</t>
-        </is>
-      </c>
-      <c r="D172" s="92" t="inlineStr">
-        <is>
-          <t>arithstd</t>
-        </is>
-      </c>
+          <t>mat_std_w</t>
+        </is>
+      </c>
+      <c r="D172" s="92" t="n"/>
       <c r="E172" s="11" t="inlineStr">
         <is>
-          <t>WAIS-IV Arithmétique — Note standard</t>
+          <t>WAIS-IV Matrices — Note standard</t>
         </is>
       </c>
       <c r="F172" s="11" t="inlineStr">
         <is>
-          <t>Numérique ; SZ+DR seulement</t>
+          <t>Numérique (note standard)</t>
         </is>
       </c>
       <c r="G172" s="92" t="n">
@@ -13460,42 +13456,42 @@
       </c>
       <c r="I172" s="11" t="inlineStr">
         <is>
-          <t>FEATURE (supplementary; SZ + DR only — BP absent). Mental arithmetic under working-memory load (WAIS Arithmetic: solve spoken word problems without paper). A Working Memory Index subtest tapping verbal working memory, attention and numerical manipulation. Age-normed scaled score (mean 10 / SD 3); cohort-limited, so a sensitivity feature.</t>
+          <t>FEATURE (supplementary; BP + SZ only — DR absent). Nonverbal fluid / perceptual reasoning (WAIS Matrix Reasoning: complete a visual pattern). Core Perceptual Reasoning subtest; complements verbal reasoning with a culture-light fluid-intelligence measure. Age-normed scaled score (mean 10 / SD 3). Usable in masked FA, but its cohort-aligned missingness makes it a sensitivity feature, not part of the all-cohort stratification core.</t>
         </is>
       </c>
       <c r="J172" s="11" t="inlineStr">
         <is>
-          <t>int8 ordinal</t>
+          <t>float</t>
         </is>
       </c>
       <c r="K172" s="11" t="inlineStr">
         <is>
-          <t>[no data available]</t>
-        </is>
-      </c>
-      <c r="L172" s="69" t="inlineStr">
-        <is>
-          <t>NOT USABLE — 2-cohort sensitivity-only (WAIS arithmetic); excluded from main matrix</t>
+          <t>mmHg</t>
+        </is>
+      </c>
+      <c r="L172" s="12" t="inlineStr">
+        <is>
+          <t>NOT USABLE — 2-cohort sensitivity-only (WAIS matrices); excluded from main 3-cohort matrix per neuropsy_features.yaml</t>
         </is>
       </c>
       <c r="M172" s="11" t="inlineStr">
         <is>
-          <t>arithstd_w</t>
+          <t>mat_std_w</t>
         </is>
       </c>
       <c r="N172" s="22" t="inlineStr">
         <is>
-          <t>2 (SZ/DR)</t>
+          <t>2 (BP/SZ)</t>
         </is>
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>Masked-FA feature; cohort-missing risk; cap [1,19].</t>
+          <t>Masked-FA feature; cohort-missing risk for stratification; cap [1,19].</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Scaled score; SZ+DR only (BP absent)</t>
+          <t>Scaled score; BP+SZ only (DR absent)</t>
         </is>
       </c>
     </row>
@@ -13507,22 +13503,22 @@
       </c>
       <c r="B173" s="11" t="inlineStr">
         <is>
-          <t>code04_w</t>
+          <t>nstand_w</t>
         </is>
       </c>
       <c r="C173" s="11" t="inlineStr">
         <is>
-          <t>sdmt0101_w</t>
+          <t>nstand_w</t>
         </is>
       </c>
       <c r="D173" s="92" t="inlineStr">
         <is>
-          <t>code04</t>
+          <t>nstand</t>
         </is>
       </c>
       <c r="E173" s="11" t="inlineStr">
         <is>
-          <t>WAIS Coding / SDMT (processing speed), standard score</t>
+          <t>WAIS Digit Span (working memory), standard score</t>
         </is>
       </c>
       <c r="F173" s="11" t="inlineStr">
@@ -13538,7 +13534,7 @@
       </c>
       <c r="I173" s="11" t="inlineStr">
         <is>
-          <t>CORE FEATURE — graphomotor processing speed and incidental associative learning (WAIS Coding / Digit-Symbol: copy symbols paired with digits against the clock). A principal Processing Speed subtest and one of the most consistently impaired cognitive measures across psychiatric disorders. Age-normed scaled score (mean 10 / SD 3) in all three cohorts; anchors the processing-speed dimension.</t>
+          <t>CORE FEATURE — auditory-verbal short-term and working memory (WAIS Digit Span: repeat digit sequences forward, backward, and in order). The canonical working-memory subtest and a domain central to trans-diagnostic cognitive impairment. The age-normed scaled score is comparable across all three cohorts; the standard score is used because BP's raw span values are corrupted. Anchors the working-memory dimension.</t>
         </is>
       </c>
       <c r="J173" s="11" t="inlineStr">
@@ -13548,7 +13544,7 @@
       </c>
       <c r="K173" s="11" t="inlineStr">
         <is>
-          <t>WAIS Coding / SDMT scaled score (1-19)</t>
+          <t>WAIS Digit Span scaled score (1-19)</t>
         </is>
       </c>
       <c r="L173" s="12" t="inlineStr">
@@ -13558,7 +13554,7 @@
       </c>
       <c r="M173" s="11" t="inlineStr">
         <is>
-          <t>wais_code_std</t>
+          <t>wais_digitspan_std</t>
         </is>
       </c>
       <c r="N173" s="22" t="inlineStr">
@@ -13568,12 +13564,12 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>SZ uses SDMT (sdmt0101_w) as the processing-speed standard score</t>
+          <t>Standard score only (BP raw nbrut_w corrupted)</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Scaled score all 3 cohorts</t>
+          <t>Scaled score all 3; BP raw corrupted but standard score clean</t>
         </is>
       </c>
     </row>
@@ -13583,25 +13579,25 @@
           <t>NEUROPSYCHOLOGIE</t>
         </is>
       </c>
-      <c r="B174" s="11" t="inlineStr">
-        <is>
-          <t>symbol04_w</t>
-        </is>
-      </c>
-      <c r="C174" s="11" t="n"/>
+      <c r="B174" s="11" t="n"/>
+      <c r="C174" s="11" t="inlineStr">
+        <is>
+          <t>arithstd_w</t>
+        </is>
+      </c>
       <c r="D174" s="92" t="inlineStr">
         <is>
-          <t>symbol04</t>
+          <t>arithstd</t>
         </is>
       </c>
       <c r="E174" s="11" t="inlineStr">
         <is>
-          <t>WAIS-IV Symboles — Note standard</t>
+          <t>WAIS-IV Arithmétique — Note standard</t>
         </is>
       </c>
       <c r="F174" s="11" t="inlineStr">
         <is>
-          <t>Numérique (note standard) ; BP+DR seulement</t>
+          <t>Numérique ; SZ+DR seulement</t>
         </is>
       </c>
       <c r="G174" s="92" t="n">
@@ -13612,329 +13608,345 @@
       </c>
       <c r="I174" s="11" t="inlineStr">
         <is>
+          <t>FEATURE (supplementary; SZ + DR only — BP absent). Mental arithmetic under working-memory load (WAIS Arithmetic: solve spoken word problems without paper). A Working Memory Index subtest tapping verbal working memory, attention and numerical manipulation. Age-normed scaled score (mean 10 / SD 3); cohort-limited, so a sensitivity feature.</t>
+        </is>
+      </c>
+      <c r="J174" s="11" t="inlineStr">
+        <is>
+          <t>int8 ordinal</t>
+        </is>
+      </c>
+      <c r="K174" s="11" t="inlineStr">
+        <is>
+          <t>[no data available]</t>
+        </is>
+      </c>
+      <c r="L174" s="69" t="inlineStr">
+        <is>
+          <t>NOT USABLE — 2-cohort sensitivity-only (WAIS arithmetic); excluded from main matrix</t>
+        </is>
+      </c>
+      <c r="M174" s="11" t="inlineStr">
+        <is>
+          <t>arithstd_w</t>
+        </is>
+      </c>
+      <c r="N174" s="22" t="inlineStr">
+        <is>
+          <t>2 (SZ/DR)</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>Masked-FA feature; cohort-missing risk; cap [1,19].</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>Scaled score; SZ+DR only (BP absent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="21" customFormat="1" customHeight="1" s="13">
+      <c r="A175" s="11" t="inlineStr">
+        <is>
+          <t>NEUROPSYCHOLOGIE</t>
+        </is>
+      </c>
+      <c r="B175" s="11" t="inlineStr">
+        <is>
+          <t>code04_w</t>
+        </is>
+      </c>
+      <c r="C175" s="11" t="inlineStr">
+        <is>
+          <t>sdmt0101_w</t>
+        </is>
+      </c>
+      <c r="D175" s="92" t="inlineStr">
+        <is>
+          <t>code04</t>
+        </is>
+      </c>
+      <c r="E175" s="11" t="inlineStr">
+        <is>
+          <t>WAIS Coding / SDMT (processing speed), standard score</t>
+        </is>
+      </c>
+      <c r="F175" s="11" t="inlineStr">
+        <is>
+          <t>Numérique (note standard)</t>
+        </is>
+      </c>
+      <c r="G175" s="92" t="n">
+        <v>1</v>
+      </c>
+      <c r="H175" s="119" t="n">
+        <v>19</v>
+      </c>
+      <c r="I175" s="11" t="inlineStr">
+        <is>
+          <t>CORE FEATURE — graphomotor processing speed and incidental associative learning (WAIS Coding / Digit-Symbol: copy symbols paired with digits against the clock). A principal Processing Speed subtest and one of the most consistently impaired cognitive measures across psychiatric disorders. Age-normed scaled score (mean 10 / SD 3) in all three cohorts; anchors the processing-speed dimension.</t>
+        </is>
+      </c>
+      <c r="J175" s="11" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="K175" s="11" t="inlineStr">
+        <is>
+          <t>WAIS Coding / SDMT scaled score (1-19)</t>
+        </is>
+      </c>
+      <c r="L175" s="12" t="inlineStr">
+        <is>
+          <t>READY — Comparable in 3 cohorts (Tier A); neuropsy_features.yaml 2026-05-30</t>
+        </is>
+      </c>
+      <c r="M175" s="11" t="inlineStr">
+        <is>
+          <t>wais_code_std</t>
+        </is>
+      </c>
+      <c r="N175" s="22" t="inlineStr">
+        <is>
+          <t>3 (BP/SZ/DR)</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>SZ uses SDMT (sdmt0101_w) as the processing-speed standard score</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>Scaled score all 3 cohorts</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="21" customFormat="1" customHeight="1" s="13">
+      <c r="A176" s="11" t="inlineStr">
+        <is>
+          <t>NEUROPSYCHOLOGIE</t>
+        </is>
+      </c>
+      <c r="B176" s="11" t="inlineStr">
+        <is>
+          <t>symbol04_w</t>
+        </is>
+      </c>
+      <c r="C176" s="11" t="n"/>
+      <c r="D176" s="92" t="inlineStr">
+        <is>
+          <t>symbol04</t>
+        </is>
+      </c>
+      <c r="E176" s="11" t="inlineStr">
+        <is>
+          <t>WAIS-IV Symboles — Note standard</t>
+        </is>
+      </c>
+      <c r="F176" s="11" t="inlineStr">
+        <is>
+          <t>Numérique (note standard) ; BP+DR seulement</t>
+        </is>
+      </c>
+      <c r="G176" s="92" t="n">
+        <v>1</v>
+      </c>
+      <c r="H176" s="119" t="n">
+        <v>19</v>
+      </c>
+      <c r="I176" s="11" t="inlineStr">
+        <is>
           <t>FEATURE (supplementary; BP + DR only — SZ absent). Visual scanning and processing speed (WAIS Symbol Search: decide whether target symbols appear in a search array). The second Processing Speed subtest, converging with Coding. Age-normed scaled score (mean 10 / SD 3); cohort-limited, so a sensitivity feature.</t>
         </is>
       </c>
-      <c r="J174" s="11" t="inlineStr">
+      <c r="J176" s="11" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="K174" s="11" t="inlineStr">
+      <c r="K176" s="11" t="inlineStr">
         <is>
           <t>mmHg</t>
         </is>
       </c>
-      <c r="L174" s="69" t="inlineStr">
+      <c r="L176" s="69" t="inlineStr">
         <is>
           <t>NOT USABLE — 2-cohort sensitivity-only (WAIS symbols); excluded from main matrix</t>
         </is>
       </c>
-      <c r="M174" s="11" t="inlineStr">
+      <c r="M176" s="11" t="inlineStr">
         <is>
           <t>symbol04_w</t>
         </is>
       </c>
-      <c r="N174" s="22" t="inlineStr">
+      <c r="N176" s="22" t="inlineStr">
         <is>
           <t>2 (BP/DR)</t>
         </is>
       </c>
-      <c r="O174" t="inlineStr">
+      <c r="O176" t="inlineStr">
         <is>
           <t>Masked-FA feature; cohort-missing risk; cap [1,19].</t>
         </is>
       </c>
-      <c r="P174" t="inlineStr">
+      <c r="P176" t="inlineStr">
         <is>
           <t>Scaled score; BP+DR only (SZ absent)</t>
         </is>
       </c>
     </row>
-    <row r="175" ht="21" customFormat="1" customHeight="1" s="13">
-      <c r="A175" s="70" t="inlineStr">
+    <row r="177" ht="21" customFormat="1" customHeight="1" s="13">
+      <c r="A177" s="70" t="inlineStr">
         <is>
           <t>EVALUATION MEDICALE</t>
         </is>
       </c>
-      <c r="B175" s="70" t="inlineStr">
+      <c r="B177" s="70" t="inlineStr">
         <is>
           <t>agetrt</t>
         </is>
       </c>
-      <c r="C175" s="70" t="inlineStr">
+      <c r="C177" s="70" t="inlineStr">
         <is>
           <t>agetrt</t>
         </is>
       </c>
-      <c r="D175" s="104" t="inlineStr">
+      <c r="D177" s="104" t="inlineStr">
         <is>
           <t>agetrt</t>
         </is>
       </c>
-      <c r="E175" s="70" t="inlineStr">
+      <c r="E177" s="70" t="inlineStr">
         <is>
           <t>Âge du patient au premier traitement psychotrope/antipsychotique</t>
         </is>
       </c>
-      <c r="F175" s="70" t="inlineStr">
+      <c r="F177" s="70" t="inlineStr">
         <is>
           <t>Numérique (années) ; BP=psychotrope, SZ=antipsychotique, DR=psychotrope (libellés diffèrent)</t>
         </is>
       </c>
-      <c r="G175" s="104" t="n">
+      <c r="G177" s="104" t="n">
         <v>5</v>
       </c>
-      <c r="H175" s="133" t="n">
+      <c r="H177" s="133" t="n">
         <v>90</v>
       </c>
-      <c r="I175" s="70" t="inlineStr">
+      <c r="I177" s="70" t="inlineStr">
         <is>
           <t>Age at first psychiatric medication exposure : a trans-diagnostic illness-trajectory anchor. Early treatment exposure is associated with more severe course and shapes neurodevelopmental cognitive trajectories. The single verbatim Tier-A variable across all three thesauri in this tab.</t>
         </is>
       </c>
-      <c r="J175" s="70" t="inlineStr">
+      <c r="J177" s="70" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="K175" s="70" t="inlineStr">
+      <c r="K177" s="70" t="inlineStr">
         <is>
           <t>years</t>
         </is>
       </c>
-      <c r="L175" s="71" t="inlineStr">
+      <c r="L177" s="71" t="inlineStr">
         <is>
           <t>READY — Comparable construct in all 3 cohorts and data present in all 3 CSVs</t>
         </is>
       </c>
-      <c r="M175" s="70" t="inlineStr">
+      <c r="M177" s="70" t="inlineStr">
         <is>
           <t>agetrt</t>
         </is>
       </c>
-      <c r="N175" s="22" t="inlineStr">
+      <c r="N177" s="22" t="inlineStr">
         <is>
           <t>3 (BP/SZ/DR)</t>
         </is>
       </c>
-      <c r="O175" t="inlineStr">
+      <c r="O177" t="inlineStr">
         <is>
           <t>[retained as PRIMARY FEATURE: course/staging anchor, present in all 3 cohorts, not a DSM-5 criterion; note cross-cohort anchor differs — see Codage]</t>
         </is>
       </c>
     </row>
-    <row r="176" ht="21" customFormat="1" customHeight="1" s="13">
-      <c r="A176" s="70" t="inlineStr">
+    <row r="178" ht="21" customFormat="1" customHeight="1" s="13">
+      <c r="A178" s="70" t="inlineStr">
         <is>
           <t>EVALUATION MEDICALE</t>
         </is>
       </c>
-      <c r="B176" s="70" t="inlineStr">
+      <c r="B178" s="70" t="inlineStr">
         <is>
           <t>agedebutpremier_episode</t>
         </is>
       </c>
-      <c r="C176" s="70" t="inlineStr">
+      <c r="C178" s="70" t="inlineStr">
         <is>
           <t>agepisod</t>
         </is>
       </c>
-      <c r="D176" s="104" t="inlineStr">
+      <c r="D178" s="104" t="inlineStr">
         <is>
           <t>agedebutpremier_episode</t>
         </is>
       </c>
-      <c r="E176" s="70" t="inlineStr">
+      <c r="E178" s="70" t="inlineStr">
         <is>
           <t>Âge au premier épisode (mood pour BP/DR, psychotique pour SZ)</t>
         </is>
       </c>
-      <c r="F176" s="70" t="inlineStr">
+      <c r="F178" s="70" t="inlineStr">
         <is>
           <t>Numérique (années) ; BP/DR=premier épisode thymique (EDM/manie/hypomanie/mixte), SZ=premier épisode psychotique caractérisé</t>
         </is>
       </c>
-      <c r="G176" s="104" t="n">
+      <c r="G178" s="104" t="n">
         <v>5</v>
       </c>
-      <c r="H176" s="133" t="n">
+      <c r="H178" s="133" t="n">
         <v>90</v>
       </c>
-      <c r="I176" s="70" t="inlineStr">
+      <c r="I178" s="70" t="inlineStr">
         <is>
           <t>Age at illness onset : aligned across pathologies as the canonical clinical-onset variable, even though the qualifying episode type differs (mood vs psychotic). Early onset (&lt; 21 ans) is a robust trans-diagnostic severity marker and a key clustering variable for illness-trajectory phenotypes.</t>
         </is>
       </c>
-      <c r="J176" s="70" t="inlineStr">
+      <c r="J178" s="70" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="K176" s="70" t="inlineStr">
+      <c r="K178" s="70" t="inlineStr">
         <is>
           <t>years</t>
         </is>
       </c>
-      <c r="L176" s="71" t="inlineStr">
+      <c r="L178" s="71" t="inlineStr">
         <is>
           <t>READY — Comparable construct in all 3 cohorts and data present in all 3 CSVs</t>
         </is>
       </c>
-      <c r="M176" s="70" t="inlineStr">
+      <c r="M178" s="70" t="inlineStr">
         <is>
           <t>agedebutpremier_episode</t>
         </is>
       </c>
-      <c r="N176" s="22" t="inlineStr">
+      <c r="N178" s="22" t="inlineStr">
         <is>
           <t>3 (BP/SZ/DR)</t>
         </is>
       </c>
-      <c r="O176" t="inlineStr">
+      <c r="O178" t="inlineStr">
         <is>
           <t>POOL as 'age at first illness episode' (years). Document per-cohort interpretation: BP/DR=first mood episode, SZ=first psychotic episode. Cohort indicator covariate optional in clustering. [retained as PRIMARY FEATURE: course/staging anchor, present in all 3 cohorts, not a DSM-5 criterion; note cross-cohort anchor differs — see Codage]</t>
         </is>
       </c>
-      <c r="P176" t="inlineStr">
+      <c r="P178" t="inlineStr">
         <is>
           <t>✓ COMPARABLE per data. BP mood-onset median=20 (n=4919), SZ psychotic-onset median=20 (n=2032), DR mood-onset median=31 (n=285). BP and SZ have similar central tendency; DR's later median reflects depression's later epidemiological onset (clinically expected). All three measure the same biological construct: age at first illness episode.</t>
-        </is>
-      </c>
-    </row>
-    <row r="177" ht="21" customFormat="1" customHeight="1" s="13">
-      <c r="A177" s="2" t="inlineStr">
-        <is>
-          <t>ANTECEDENTS</t>
-        </is>
-      </c>
-      <c r="B177" s="2" t="inlineStr">
-        <is>
-          <t>migraine_mhoccur</t>
-        </is>
-      </c>
-      <c r="C177" s="2" t="inlineStr">
-        <is>
-          <t>migraine_mhoccur</t>
-        </is>
-      </c>
-      <c r="D177" s="89" t="inlineStr">
-        <is>
-          <t>migraine_mhoccur</t>
-        </is>
-      </c>
-      <c r="E177" s="2" t="inlineStr">
-        <is>
-          <t>Migraine (occurrence)</t>
-        </is>
-      </c>
-      <c r="F177" s="2" t="inlineStr">
-        <is>
-          <t>Y/N/U (BP/SZ) ; codages similaires en DR</t>
-        </is>
-      </c>
-      <c r="G177" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="H177" s="117" t="n">
-        <v>1</v>
-      </c>
-      <c r="I177" s="2" t="inlineStr">
-        <is>
-          <t>Migraine is a strong transdiagnostic somatic comorbidity in mood and psychotic disorders, with shared neurovascular and neuroinflammatory mechanisms; prevalence is elevated (~30%) in bipolar and depressive disorders.</t>
-        </is>
-      </c>
-      <c r="J177" s="2" t="inlineStr">
-        <is>
-          <t>int8 binary</t>
-        </is>
-      </c>
-      <c r="K177" s="2" t="inlineStr">
-        <is>
-          <t>{0=No/Non, 1=Yes/Oui, NA=Unknown}</t>
-        </is>
-      </c>
-      <c r="L177" s="5" t="inlineStr">
-        <is>
-          <t>READY — Comparable construct in all 3 cohorts and data present in all 3 CSVs</t>
-        </is>
-      </c>
-      <c r="M177" s="2" t="inlineStr">
-        <is>
-          <t>migraine_mhoccur</t>
-        </is>
-      </c>
-      <c r="N177" s="22" t="inlineStr">
-        <is>
-          <t>3 (BP/SZ/DR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="178" ht="21" customFormat="1" customHeight="1" s="13">
-      <c r="A178" s="2" t="inlineStr">
-        <is>
-          <t>ANTECEDENTS</t>
-        </is>
-      </c>
-      <c r="B178" s="2" t="inlineStr">
-        <is>
-          <t>sep_mhoccur</t>
-        </is>
-      </c>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t>sep_mhoccur</t>
-        </is>
-      </c>
-      <c r="D178" s="89" t="inlineStr">
-        <is>
-          <t>sep_mhoccur</t>
-        </is>
-      </c>
-      <c r="E178" s="2" t="inlineStr">
-        <is>
-          <t>Sclérose en plaques (occurrence)</t>
-        </is>
-      </c>
-      <c r="F178" s="2" t="inlineStr">
-        <is>
-          <t>Y/N/U</t>
-        </is>
-      </c>
-      <c r="G178" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="H178" s="117" t="n">
-        <v>1</v>
-      </c>
-      <c r="I178" s="2" t="inlineStr">
-        <is>
-          <t>Multiple sclerosis : a major neuroinflammatory comorbidity that can present with or precede mood/psychotic symptoms. Critical to flag for differential diagnosis and for cluster analyses examining neuroimmune subtypes.</t>
-        </is>
-      </c>
-      <c r="J178" s="2" t="inlineStr">
-        <is>
-          <t>int8 binary</t>
-        </is>
-      </c>
-      <c r="K178" s="2" t="inlineStr">
-        <is>
-          <t>{0=No/Non, 1=Yes/Oui, NA=Unknown}</t>
-        </is>
-      </c>
-      <c r="L178" s="5" t="inlineStr">
-        <is>
-          <t>NOT USABLE — near-zero-variance medical-history flag (minority &lt;5%); no modelling signal</t>
-        </is>
-      </c>
-      <c r="M178" s="2" t="inlineStr">
-        <is>
-          <t>sep_mhoccur</t>
-        </is>
-      </c>
-      <c r="N178" s="22" t="inlineStr">
-        <is>
-          <t>3 (BP/SZ/DR)</t>
         </is>
       </c>
     </row>
@@ -13946,27 +13958,27 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>epilepsie_mhoccur</t>
+          <t>migraine_mhoccur</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>epilepsie_mhoccur</t>
+          <t>migraine_mhoccur</t>
         </is>
       </c>
       <c r="D179" s="89" t="inlineStr">
         <is>
-          <t>epilepsie_mhoccur</t>
+          <t>migraine_mhoccur</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>Épilepsie (occurrence)</t>
+          <t>Migraine (occurrence)</t>
         </is>
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t>Y/N/U</t>
+          <t>Y/N/U (BP/SZ) ; codages similaires en DR</t>
         </is>
       </c>
       <c r="G179" s="89" t="n">
@@ -13977,7 +13989,7 @@
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>Epilepsy : bidirectional comorbidity with psychiatric disorders (~5-10% in major mental illness); modifies antipsychotic/antidepressant prescribing and lithium/valproate use; cluster-relevant for neurological-psychiatric overlap phenotypes.</t>
+          <t>Migraine is a strong transdiagnostic somatic comorbidity in mood and psychotic disorders, with shared neurovascular and neuroinflammatory mechanisms; prevalence is elevated (~30%) in bipolar and depressive disorders.</t>
         </is>
       </c>
       <c r="J179" s="2" t="inlineStr">
@@ -13997,7 +14009,7 @@
       </c>
       <c r="M179" s="2" t="inlineStr">
         <is>
-          <t>epilepsie_mhoccur</t>
+          <t>migraine_mhoccur</t>
         </is>
       </c>
       <c r="N179" s="22" t="inlineStr">
@@ -14014,22 +14026,22 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>traumacra_mhoccur</t>
+          <t>sep_mhoccur</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>traumacra_mhoccur</t>
+          <t>sep_mhoccur</t>
         </is>
       </c>
       <c r="D180" s="89" t="inlineStr">
         <is>
-          <t>traumacra_mhoccur</t>
+          <t>sep_mhoccur</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>Traumatisme crânien (occurrence)</t>
+          <t>Sclérose en plaques (occurrence)</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr">
@@ -14045,7 +14057,7 @@
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>History of head injury / TBI : established risk factor for mood disorders, psychosis, and cognitive impairment; key environmental modifier for clustering on neuropsychiatric severity.</t>
+          <t>Multiple sclerosis : a major neuroinflammatory comorbidity that can present with or precede mood/psychotic symptoms. Critical to flag for differential diagnosis and for cluster analyses examining neuroimmune subtypes.</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr">
@@ -14060,12 +14072,12 @@
       </c>
       <c r="L180" s="5" t="inlineStr">
         <is>
-          <t>READY — Comparable construct in all 3 cohorts and data present in all 3 CSVs</t>
+          <t>NOT USABLE — near-zero-variance medical-history flag (minority &lt;5%); no modelling signal</t>
         </is>
       </c>
       <c r="M180" s="2" t="inlineStr">
         <is>
-          <t>traumacra_mhoccur</t>
+          <t>sep_mhoccur</t>
         </is>
       </c>
       <c r="N180" s="22" t="inlineStr">
@@ -14082,22 +14094,22 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>avc_mhoccur</t>
+          <t>epilepsie_mhoccur</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>avc_mhoccur</t>
+          <t>epilepsie_mhoccur</t>
         </is>
       </c>
       <c r="D181" s="89" t="inlineStr">
         <is>
-          <t>avc_mhoccur</t>
+          <t>epilepsie_mhoccur</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>Accident Vasculaire Cérébral (occurrence)</t>
+          <t>Épilepsie (occurrence)</t>
         </is>
       </c>
       <c r="F181" s="2" t="inlineStr">
@@ -14113,7 +14125,7 @@
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>Stroke history : both a cause of vascular depression/psychosis and a comorbidity in older psychiatric patients; central cardiovascular-brain axis variable for clustering.</t>
+          <t>Epilepsy : bidirectional comorbidity with psychiatric disorders (~5-10% in major mental illness); modifies antipsychotic/antidepressant prescribing and lithium/valproate use; cluster-relevant for neurological-psychiatric overlap phenotypes.</t>
         </is>
       </c>
       <c r="J181" s="2" t="inlineStr">
@@ -14128,12 +14140,12 @@
       </c>
       <c r="L181" s="5" t="inlineStr">
         <is>
-          <t>NOT USABLE — near-zero-variance medical-history flag (minority &lt;5%); no modelling signal</t>
+          <t>READY — Comparable construct in all 3 cohorts and data present in all 3 CSVs</t>
         </is>
       </c>
       <c r="M181" s="2" t="inlineStr">
         <is>
-          <t>avc_mhoccur</t>
+          <t>epilepsie_mhoccur</t>
         </is>
       </c>
       <c r="N181" s="22" t="inlineStr">
@@ -14150,22 +14162,22 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>autneuro_mhoccur</t>
+          <t>traumacra_mhoccur</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>autneuro_mhoccur</t>
+          <t>traumacra_mhoccur</t>
         </is>
       </c>
       <c r="D182" s="89" t="inlineStr">
         <is>
-          <t>autneuro_mhoccur</t>
+          <t>traumacra_mhoccur</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>Autre maladie neurologique (occurrence)</t>
+          <t>Traumatisme crânien (occurrence)</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr">
@@ -14181,7 +14193,7 @@
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>Other neurological disease : catch-all flag for atypical neurological comorbidities not captured by specific codes; flags neurological-psychiatric overlap that warrants stratification.</t>
+          <t>History of head injury / TBI : established risk factor for mood disorders, psychosis, and cognitive impairment; key environmental modifier for clustering on neuropsychiatric severity.</t>
         </is>
       </c>
       <c r="J182" s="2" t="inlineStr">
@@ -14201,7 +14213,7 @@
       </c>
       <c r="M182" s="2" t="inlineStr">
         <is>
-          <t>autneuro_mhoccur</t>
+          <t>traumacra_mhoccur</t>
         </is>
       </c>
       <c r="N182" s="22" t="inlineStr">
@@ -14218,27 +14230,27 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>hta_mhoccur</t>
+          <t>avc_mhoccur</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>hta_mhoccur</t>
+          <t>avc_mhoccur</t>
         </is>
       </c>
       <c r="D183" s="89" t="inlineStr">
         <is>
-          <t>hta_mhoccur</t>
+          <t>avc_mhoccur</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>Hypertension artérielle (occurrence)</t>
+          <t>Accident Vasculaire Cérébral (occurrence)</t>
         </is>
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>Y/N/U ; libellé DR='HTA'</t>
+          <t>Y/N/U</t>
         </is>
       </c>
       <c r="G183" s="89" t="n">
@@ -14249,7 +14261,7 @@
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>Hypertension : central cardiovascular comorbidity; key element of metabolic-cardiovascular syndrome elevated in bipolar/depression and aggravated by antipsychotic exposure in schizophrenia.</t>
+          <t>Stroke history : both a cause of vascular depression/psychosis and a comorbidity in older psychiatric patients; central cardiovascular-brain axis variable for clustering.</t>
         </is>
       </c>
       <c r="J183" s="2" t="inlineStr">
@@ -14264,12 +14276,12 @@
       </c>
       <c r="L183" s="5" t="inlineStr">
         <is>
-          <t>READY — Comparable construct in all 3 cohorts and data present in all 3 CSVs</t>
+          <t>NOT USABLE — near-zero-variance medical-history flag (minority &lt;5%); no modelling signal</t>
         </is>
       </c>
       <c r="M183" s="2" t="inlineStr">
         <is>
-          <t>hta_mhoccur</t>
+          <t>avc_mhoccur</t>
         </is>
       </c>
       <c r="N183" s="22" t="inlineStr">
@@ -14286,27 +14298,27 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>coronar_mhoccur</t>
+          <t>autneuro_mhoccur</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>coronar_mhoccur</t>
+          <t>autneuro_mhoccur</t>
         </is>
       </c>
       <c r="D184" s="89" t="inlineStr">
         <is>
-          <t>coronar_mhoccur</t>
+          <t>autneuro_mhoccur</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>Maladie coronarienne (occurrence)</t>
+          <t>Autre maladie neurologique (occurrence)</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>Y/N/U ; DR précise 'hors IDM' dans le libellé</t>
+          <t>Y/N/U</t>
         </is>
       </c>
       <c r="G184" s="89" t="n">
@@ -14317,7 +14329,7 @@
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>Coronary artery disease : major cardiovascular endpoint with elevated risk in severe mental illness (relative risk 2-3x); critical mortality-risk variable for clustering.</t>
+          <t>Other neurological disease : catch-all flag for atypical neurological comorbidities not captured by specific codes; flags neurological-psychiatric overlap that warrants stratification.</t>
         </is>
       </c>
       <c r="J184" s="2" t="inlineStr">
@@ -14332,12 +14344,12 @@
       </c>
       <c r="L184" s="5" t="inlineStr">
         <is>
-          <t>NOT USABLE — near-zero-variance medical-history flag (minority &lt;5%); no modelling signal</t>
+          <t>READY — Comparable construct in all 3 cohorts and data present in all 3 CSVs</t>
         </is>
       </c>
       <c r="M184" s="2" t="inlineStr">
         <is>
-          <t>coronar_mhoccur</t>
+          <t>autneuro_mhoccur</t>
         </is>
       </c>
       <c r="N184" s="22" t="inlineStr">
@@ -14354,27 +14366,27 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>infarctus_mhoccur</t>
+          <t>hta_mhoccur</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>infarctus_mhoccur</t>
+          <t>hta_mhoccur</t>
         </is>
       </c>
       <c r="D185" s="89" t="inlineStr">
         <is>
-          <t>infarctus_mhoccur</t>
+          <t>hta_mhoccur</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>Infarctus du myocarde (occurrence)</t>
+          <t>Hypertension artérielle (occurrence)</t>
         </is>
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>Y/N/U</t>
+          <t>Y/N/U ; libellé DR='HTA'</t>
         </is>
       </c>
       <c r="G185" s="89" t="n">
@@ -14385,7 +14397,7 @@
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>Myocardial infarction history : hard cardiovascular endpoint, prognostically distinct from coronary disease without MI; flags high-risk subgroup for medication choice and outcome stratification.</t>
+          <t>Hypertension : central cardiovascular comorbidity; key element of metabolic-cardiovascular syndrome elevated in bipolar/depression and aggravated by antipsychotic exposure in schizophrenia.</t>
         </is>
       </c>
       <c r="J185" s="2" t="inlineStr">
@@ -14400,12 +14412,12 @@
       </c>
       <c r="L185" s="5" t="inlineStr">
         <is>
-          <t>NOT USABLE — near-zero-variance medical-history flag (minority &lt;5%); no modelling signal</t>
+          <t>READY — Comparable construct in all 3 cohorts and data present in all 3 CSVs</t>
         </is>
       </c>
       <c r="M185" s="2" t="inlineStr">
         <is>
-          <t>infarctus_mhoccur</t>
+          <t>hta_mhoccur</t>
         </is>
       </c>
       <c r="N185" s="22" t="inlineStr">
@@ -14422,27 +14434,27 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>trbrycard_mhoccur</t>
+          <t>coronar_mhoccur</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>trbrycard_mhoccur</t>
+          <t>coronar_mhoccur</t>
         </is>
       </c>
       <c r="D186" s="89" t="inlineStr">
         <is>
-          <t>trbrycard_mhoccur</t>
+          <t>coronar_mhoccur</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>Trouble du rythme cardiaque (occurrence)</t>
+          <t>Maladie coronarienne (occurrence)</t>
         </is>
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>Y/N/U</t>
+          <t>Y/N/U ; DR précise 'hors IDM' dans le libellé</t>
         </is>
       </c>
       <c r="G186" s="89" t="n">
@@ -14453,7 +14465,7 @@
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>Cardiac arrhythmia : relevant for QTc-prolonging antipsychotic / antidepressant safety, lithium toxicity monitoring, and cardiovascular phenotyping in clustering.</t>
+          <t>Coronary artery disease : major cardiovascular endpoint with elevated risk in severe mental illness (relative risk 2-3x); critical mortality-risk variable for clustering.</t>
         </is>
       </c>
       <c r="J186" s="2" t="inlineStr">
@@ -14473,7 +14485,7 @@
       </c>
       <c r="M186" s="2" t="inlineStr">
         <is>
-          <t>trbrycard_mhoccur</t>
+          <t>coronar_mhoccur</t>
         </is>
       </c>
       <c r="N186" s="22" t="inlineStr">
@@ -14490,22 +14502,22 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>autcardv_mhoccur</t>
+          <t>infarctus_mhoccur</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>autcardv_mhoccur</t>
+          <t>infarctus_mhoccur</t>
         </is>
       </c>
       <c r="D187" s="89" t="inlineStr">
         <is>
-          <t>autcardv_mhoccur</t>
+          <t>infarctus_mhoccur</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>Autre maladie cardio-vasculaire (occurrence)</t>
+          <t>Infarctus du myocarde (occurrence)</t>
         </is>
       </c>
       <c r="F187" s="2" t="inlineStr">
@@ -14521,7 +14533,7 @@
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>Other cardiovascular disease : catch-all flag for cardiovascular comorbidities outside the listed categories (e.g., valvulopathy, peripheral artery disease, heart failure).</t>
+          <t>Myocardial infarction history : hard cardiovascular endpoint, prognostically distinct from coronary disease without MI; flags high-risk subgroup for medication choice and outcome stratification.</t>
         </is>
       </c>
       <c r="J187" s="2" t="inlineStr">
@@ -14536,12 +14548,12 @@
       </c>
       <c r="L187" s="5" t="inlineStr">
         <is>
-          <t>READY — Comparable construct in all 3 cohorts and data present in all 3 CSVs</t>
+          <t>NOT USABLE — near-zero-variance medical-history flag (minority &lt;5%); no modelling signal</t>
         </is>
       </c>
       <c r="M187" s="2" t="inlineStr">
         <is>
-          <t>autcardv_mhoccur</t>
+          <t>infarctus_mhoccur</t>
         </is>
       </c>
       <c r="N187" s="22" t="inlineStr">
@@ -14558,22 +14570,22 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>autendoc_mhoccur</t>
+          <t>trbrycard_mhoccur</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>autendoc_mhoccur</t>
+          <t>trbrycard_mhoccur</t>
         </is>
       </c>
       <c r="D188" s="89" t="inlineStr">
         <is>
-          <t>autendoc_mhoccur</t>
+          <t>trbrycard_mhoccur</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>Autres endocrinopathies (occurrence)</t>
+          <t>Trouble du rythme cardiaque (occurrence)</t>
         </is>
       </c>
       <c r="F188" s="2" t="inlineStr">
@@ -14589,7 +14601,7 @@
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>Other endocrinopathy : catch-all for thyroid/adrenal/pituitary/parathyroid disorders not specifically captured; relevant for HPA axis and metabolic subtyping.</t>
+          <t>Cardiac arrhythmia : relevant for QTc-prolonging antipsychotic / antidepressant safety, lithium toxicity monitoring, and cardiovascular phenotyping in clustering.</t>
         </is>
       </c>
       <c r="J188" s="2" t="inlineStr">
@@ -14604,12 +14616,12 @@
       </c>
       <c r="L188" s="5" t="inlineStr">
         <is>
-          <t>READY — Comparable construct in all 3 cohorts and data present in all 3 CSVs</t>
+          <t>NOT USABLE — near-zero-variance medical-history flag (minority &lt;5%); no modelling signal</t>
         </is>
       </c>
       <c r="M188" s="2" t="inlineStr">
         <is>
-          <t>autendoc_mhoccur</t>
+          <t>trbrycard_mhoccur</t>
         </is>
       </c>
       <c r="N188" s="22" t="inlineStr">
@@ -14626,22 +14638,22 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>acne_mhoccur</t>
+          <t>autcardv_mhoccur</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>acne_mhoccur</t>
+          <t>autcardv_mhoccur</t>
         </is>
       </c>
       <c r="D189" s="89" t="inlineStr">
         <is>
-          <t>acne_mhoccur</t>
+          <t>autcardv_mhoccur</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>Acné (occurrence)</t>
+          <t>Autre maladie cardio-vasculaire (occurrence)</t>
         </is>
       </c>
       <c r="F189" s="2" t="inlineStr">
@@ -14657,7 +14669,7 @@
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>Acne : tracked because lithium and other psychotropics can trigger or worsen it; relevant for treatment tolerability phenotyping.</t>
+          <t>Other cardiovascular disease : catch-all flag for cardiovascular comorbidities outside the listed categories (e.g., valvulopathy, peripheral artery disease, heart failure).</t>
         </is>
       </c>
       <c r="J189" s="2" t="inlineStr">
@@ -14677,7 +14689,7 @@
       </c>
       <c r="M189" s="2" t="inlineStr">
         <is>
-          <t>acne_mhoccur</t>
+          <t>autcardv_mhoccur</t>
         </is>
       </c>
       <c r="N189" s="22" t="inlineStr">
@@ -14694,22 +14706,22 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>eczema_mhoccur</t>
+          <t>autendoc_mhoccur</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>eczema_mhoccur</t>
+          <t>autendoc_mhoccur</t>
         </is>
       </c>
       <c r="D190" s="89" t="inlineStr">
         <is>
-          <t>eczema_mhoccur</t>
+          <t>autendoc_mhoccur</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>Eczéma (occurrence)</t>
+          <t>Autres endocrinopathies (occurrence)</t>
         </is>
       </c>
       <c r="F190" s="2" t="inlineStr">
@@ -14725,7 +14737,7 @@
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>Eczema : marker of atopic / immune dysregulation phenotype; emerging link with bipolar and depression via inflammation pathways.</t>
+          <t>Other endocrinopathy : catch-all for thyroid/adrenal/pituitary/parathyroid disorders not specifically captured; relevant for HPA axis and metabolic subtyping.</t>
         </is>
       </c>
       <c r="J190" s="2" t="inlineStr">
@@ -14745,7 +14757,7 @@
       </c>
       <c r="M190" s="2" t="inlineStr">
         <is>
-          <t>eczema_mhoccur</t>
+          <t>autendoc_mhoccur</t>
         </is>
       </c>
       <c r="N190" s="22" t="inlineStr">
@@ -14762,22 +14774,22 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>toxidermi_mhoccur</t>
+          <t>acne_mhoccur</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>toxidermi_mhoccur</t>
+          <t>acne_mhoccur</t>
         </is>
       </c>
       <c r="D191" s="89" t="inlineStr">
         <is>
-          <t>toxidermi_mhoccur</t>
+          <t>acne_mhoccur</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>Toxidermie médicamenteuse (occurrence)</t>
+          <t>Acné (occurrence)</t>
         </is>
       </c>
       <c r="F191" s="2" t="inlineStr">
@@ -14793,7 +14805,7 @@
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>Drug-induced skin reaction history : critical safety variable — patients with previous toxidermie are at high risk on lamotrigine, carbamazepine, anticonvulsants; cluster-relevant for medication choice.</t>
+          <t>Acne : tracked because lithium and other psychotropics can trigger or worsen it; relevant for treatment tolerability phenotyping.</t>
         </is>
       </c>
       <c r="J191" s="2" t="inlineStr">
@@ -14813,7 +14825,7 @@
       </c>
       <c r="M191" s="2" t="inlineStr">
         <is>
-          <t>toxidermi_mhoccur</t>
+          <t>acne_mhoccur</t>
         </is>
       </c>
       <c r="N191" s="22" t="inlineStr">
@@ -14830,22 +14842,22 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>cheveux_mhoccur</t>
+          <t>eczema_mhoccur</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>cheveux_mhoccur</t>
+          <t>eczema_mhoccur</t>
         </is>
       </c>
       <c r="D192" s="89" t="inlineStr">
         <is>
-          <t>cheveux_mhoccur</t>
+          <t>eczema_mhoccur</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>Perte importante de cheveux (occurrence)</t>
+          <t>Eczéma (occurrence)</t>
         </is>
       </c>
       <c r="F192" s="2" t="inlineStr">
@@ -14861,7 +14873,7 @@
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>Significant hair loss : commonly induced or aggravated by valproate (Depakine) and lithium; relevant marker for medication tolerability and for clustering on adverse-effect-prone phenotypes.</t>
+          <t>Eczema : marker of atopic / immune dysregulation phenotype; emerging link with bipolar and depression via inflammation pathways.</t>
         </is>
       </c>
       <c r="J192" s="2" t="inlineStr">
@@ -14881,7 +14893,7 @@
       </c>
       <c r="M192" s="2" t="inlineStr">
         <is>
-          <t>cheveux_mhoccur</t>
+          <t>eczema_mhoccur</t>
         </is>
       </c>
       <c r="N192" s="22" t="inlineStr">
@@ -14898,27 +14910,27 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>psoriasis_mhoccur</t>
+          <t>toxidermi_mhoccur</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>psoriasis_mhoccur</t>
+          <t>toxidermi_mhoccur</t>
         </is>
       </c>
       <c r="D193" s="89" t="inlineStr">
         <is>
-          <t>psoriasis_mhoccur</t>
+          <t>toxidermi_mhoccur</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>Psoriasis (occurrence)</t>
+          <t>Toxidermie médicamenteuse (occurrence)</t>
         </is>
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
-          <t>Y/N/U ; SZ classe psoriasis dans pathologies auto-immunes</t>
+          <t>Y/N/U</t>
         </is>
       </c>
       <c r="G193" s="89" t="n">
@@ -14929,7 +14941,7 @@
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>Psoriasis : immune-mediated skin disease with elevated prevalence in psychiatric disorders; also commonly triggered or worsened by lithium — relevant for both treatment safety and immunological subtyping.</t>
+          <t>Drug-induced skin reaction history : critical safety variable — patients with previous toxidermie are at high risk on lamotrigine, carbamazepine, anticonvulsants; cluster-relevant for medication choice.</t>
         </is>
       </c>
       <c r="J193" s="2" t="inlineStr">
@@ -14949,7 +14961,7 @@
       </c>
       <c r="M193" s="2" t="inlineStr">
         <is>
-          <t>psoriasis_mhoccur</t>
+          <t>toxidermi_mhoccur</t>
         </is>
       </c>
       <c r="N193" s="22" t="inlineStr">
@@ -14966,27 +14978,27 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>somat_all</t>
+          <t>cheveux_mhoccur</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>somat_all</t>
+          <t>cheveux_mhoccur</t>
         </is>
       </c>
       <c r="D194" s="89" t="inlineStr">
         <is>
-          <t>somat_all</t>
+          <t>cheveux_mhoccur</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>Pathologies allergiques (et inflammatoires) — drapeau de section</t>
+          <t>Perte importante de cheveux (occurrence)</t>
         </is>
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t>Y/N (drapeau)</t>
+          <t>Y/N/U</t>
         </is>
       </c>
       <c r="G194" s="89" t="n">
@@ -14997,7 +15009,7 @@
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>Allergic/inflammatory pathology umbrella flag : screening variable indicating presence of any of the allergic/auto-immune diseases below; useful summary indicator.</t>
+          <t>Significant hair loss : commonly induced or aggravated by valproate (Depakine) and lithium; relevant marker for medication tolerability and for clustering on adverse-effect-prone phenotypes.</t>
         </is>
       </c>
       <c r="J194" s="2" t="inlineStr">
@@ -15017,7 +15029,7 @@
       </c>
       <c r="M194" s="2" t="inlineStr">
         <is>
-          <t>somat_all</t>
+          <t>cheveux_mhoccur</t>
         </is>
       </c>
       <c r="N194" s="22" t="inlineStr">
@@ -15034,27 +15046,27 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>inflachro_mhoccur</t>
+          <t>psoriasis_mhoccur</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>inflachro_mhoccur</t>
+          <t>psoriasis_mhoccur</t>
         </is>
       </c>
       <c r="D195" s="89" t="inlineStr">
         <is>
-          <t>inflachro_mhoccur</t>
+          <t>psoriasis_mhoccur</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>Maladies inflammatoires chroniques de l'intestin (MICI) (occurrence)</t>
+          <t>Psoriasis (occurrence)</t>
         </is>
       </c>
       <c r="F195" s="2" t="inlineStr">
         <is>
-          <t>Y/N/U</t>
+          <t>Y/N/U ; SZ classe psoriasis dans pathologies auto-immunes</t>
         </is>
       </c>
       <c r="G195" s="89" t="n">
@@ -15065,7 +15077,7 @@
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>Inflammatory bowel disease (Crohn / RCH) : autoimmune comorbidity with elevated psychiatric prevalence; gut-brain axis variable relevant for inflammation-based clustering.</t>
+          <t>Psoriasis : immune-mediated skin disease with elevated prevalence in psychiatric disorders; also commonly triggered or worsened by lithium — relevant for both treatment safety and immunological subtyping.</t>
         </is>
       </c>
       <c r="J195" s="2" t="inlineStr">
@@ -15080,12 +15092,12 @@
       </c>
       <c r="L195" s="5" t="inlineStr">
         <is>
-          <t>NOT USABLE — near-zero-variance medical-history flag (minority &lt;5%); no modelling signal</t>
+          <t>READY — Comparable construct in all 3 cohorts and data present in all 3 CSVs</t>
         </is>
       </c>
       <c r="M195" s="2" t="inlineStr">
         <is>
-          <t>inflachro_mhoccur</t>
+          <t>psoriasis_mhoccur</t>
         </is>
       </c>
       <c r="N195" s="22" t="inlineStr">
@@ -15102,27 +15114,27 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>cirrhose_mhoccur</t>
+          <t>somat_all</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>cirrhose_mhoccur</t>
+          <t>somat_all</t>
         </is>
       </c>
       <c r="D196" s="89" t="inlineStr">
         <is>
-          <t>cirrhose_mhoccur</t>
+          <t>somat_all</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>Cirrhose (occurrence)</t>
+          <t>Pathologies allergiques (et inflammatoires) — drapeau de section</t>
         </is>
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>Y/N/U</t>
+          <t>Y/N (drapeau)</t>
         </is>
       </c>
       <c r="G196" s="89" t="n">
@@ -15133,7 +15145,7 @@
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>Cirrhosis : major hepatic comorbidity often linked to alcohol use disorder or chronic viral hepatitis; modifies drug metabolism and pharmacokinetics — critical safety variable.</t>
+          <t>Allergic/inflammatory pathology umbrella flag : screening variable indicating presence of any of the allergic/auto-immune diseases below; useful summary indicator.</t>
         </is>
       </c>
       <c r="J196" s="2" t="inlineStr">
@@ -15148,12 +15160,12 @@
       </c>
       <c r="L196" s="5" t="inlineStr">
         <is>
-          <t>NOT USABLE — near-zero-variance medical-history flag (minority &lt;5%); no modelling signal</t>
+          <t>READY — Comparable construct in all 3 cohorts and data present in all 3 CSVs</t>
         </is>
       </c>
       <c r="M196" s="2" t="inlineStr">
         <is>
-          <t>cirrhose_mhoccur</t>
+          <t>somat_all</t>
         </is>
       </c>
       <c r="N196" s="22" t="inlineStr">
@@ -15170,22 +15182,22 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>ulcgasduo_mhoccur</t>
+          <t>inflachro_mhoccur</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>ulcgasduo_mhoccur</t>
+          <t>inflachro_mhoccur</t>
         </is>
       </c>
       <c r="D197" s="89" t="inlineStr">
         <is>
-          <t>ulcgasduo_mhoccur</t>
+          <t>inflachro_mhoccur</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>Ulcère gastro-duodénal (occurrence)</t>
+          <t>Maladies inflammatoires chroniques de l'intestin (MICI) (occurrence)</t>
         </is>
       </c>
       <c r="F197" s="2" t="inlineStr">
@@ -15201,7 +15213,7 @@
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>Gastroduodenal ulcer : modifies prescribing of SSRIs (bleeding risk) and AINS; relevant somatic comorbidity for cluster analyses.</t>
+          <t>Inflammatory bowel disease (Crohn / RCH) : autoimmune comorbidity with elevated psychiatric prevalence; gut-brain axis variable relevant for inflammation-based clustering.</t>
         </is>
       </c>
       <c r="J197" s="2" t="inlineStr">
@@ -15221,7 +15233,7 @@
       </c>
       <c r="M197" s="2" t="inlineStr">
         <is>
-          <t>ulcgasduo_mhoccur</t>
+          <t>inflachro_mhoccur</t>
         </is>
       </c>
       <c r="N197" s="22" t="inlineStr">
@@ -15238,22 +15250,22 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>hepmedic_mhoccur</t>
+          <t>cirrhose_mhoccur</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>hepmedic_mhoccur</t>
+          <t>cirrhose_mhoccur</t>
         </is>
       </c>
       <c r="D198" s="89" t="inlineStr">
         <is>
-          <t>hepmedic_mhoccur</t>
+          <t>cirrhose_mhoccur</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>Hépatites médicamenteuses (occurrence)</t>
+          <t>Cirrhose (occurrence)</t>
         </is>
       </c>
       <c r="F198" s="2" t="inlineStr">
@@ -15269,7 +15281,7 @@
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>Drug-induced hepatitis history : critical safety variable — flags patients at high risk of hepatotoxicity with valproate, antipsychotics, and SSRIs.</t>
+          <t>Cirrhosis : major hepatic comorbidity often linked to alcohol use disorder or chronic viral hepatitis; modifies drug metabolism and pharmacokinetics — critical safety variable.</t>
         </is>
       </c>
       <c r="J198" s="2" t="inlineStr">
@@ -15289,7 +15301,7 @@
       </c>
       <c r="M198" s="2" t="inlineStr">
         <is>
-          <t>hepmedic_mhoccur</t>
+          <t>cirrhose_mhoccur</t>
         </is>
       </c>
       <c r="N198" s="22" t="inlineStr">
@@ -15306,22 +15318,22 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>vih_mhoccur</t>
+          <t>ulcgasduo_mhoccur</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>vih_mhoccur</t>
+          <t>ulcgasduo_mhoccur</t>
         </is>
       </c>
       <c r="D199" s="89" t="inlineStr">
         <is>
-          <t>vih_mhoccur</t>
+          <t>ulcgasduo_mhoccur</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>Infection à VIH (occurrence)</t>
+          <t>Ulcère gastro-duodénal (occurrence)</t>
         </is>
       </c>
       <c r="F199" s="2" t="inlineStr">
@@ -15337,7 +15349,7 @@
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>HIV infection : major somatic comorbidity with direct CNS effects (HAND) and antiretroviral pharmacokinetic interactions; key for differential diagnosis and clustering.</t>
+          <t>Gastroduodenal ulcer : modifies prescribing of SSRIs (bleeding risk) and AINS; relevant somatic comorbidity for cluster analyses.</t>
         </is>
       </c>
       <c r="J199" s="2" t="inlineStr">
@@ -15357,7 +15369,7 @@
       </c>
       <c r="M199" s="2" t="inlineStr">
         <is>
-          <t>vih_mhoccur</t>
+          <t>ulcgasduo_mhoccur</t>
         </is>
       </c>
       <c r="N199" s="22" t="inlineStr">
@@ -15374,22 +15386,22 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>hvc_mhoccur</t>
+          <t>hepmedic_mhoccur</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>hvc_mhoccur</t>
+          <t>hepmedic_mhoccur</t>
         </is>
       </c>
       <c r="D200" s="89" t="inlineStr">
         <is>
-          <t>hvc_mhoccur</t>
+          <t>hepmedic_mhoccur</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>Hépatite virale chronique (occurrence)</t>
+          <t>Hépatites médicamenteuses (occurrence)</t>
         </is>
       </c>
       <c r="F200" s="2" t="inlineStr">
@@ -15405,7 +15417,7 @@
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>Chronic viral hepatitis : modifies hepatic drug metabolism; HCV and HBV have neuropsychiatric manifestations (depression, cognitive disturbance) including from interferon-based therapy.</t>
+          <t>Drug-induced hepatitis history : critical safety variable — flags patients at high risk of hepatotoxicity with valproate, antipsychotics, and SSRIs.</t>
         </is>
       </c>
       <c r="J200" s="2" t="inlineStr">
@@ -15425,7 +15437,7 @@
       </c>
       <c r="M200" s="2" t="inlineStr">
         <is>
-          <t>hvc_mhoccur</t>
+          <t>hepmedic_mhoccur</t>
         </is>
       </c>
       <c r="N200" s="22" t="inlineStr">
@@ -15442,22 +15454,22 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>genetique_mhoccur</t>
+          <t>vih_mhoccur</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>genetique_mhoccur</t>
+          <t>vih_mhoccur</t>
         </is>
       </c>
       <c r="D201" s="89" t="inlineStr">
         <is>
-          <t>genetique_mhoccur</t>
+          <t>vih_mhoccur</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>Maladie génétique (occurrence)</t>
+          <t>Infection à VIH (occurrence)</t>
         </is>
       </c>
       <c r="F201" s="2" t="inlineStr">
@@ -15473,7 +15485,7 @@
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>Genetic disease : flags syndromic patients (e.g., 22q11.2 deletion, fragile X, Huntington) whose psychiatric presentation is part of a known syndrome — important to stratify in clustering.</t>
+          <t>HIV infection : major somatic comorbidity with direct CNS effects (HAND) and antiretroviral pharmacokinetic interactions; key for differential diagnosis and clustering.</t>
         </is>
       </c>
       <c r="J201" s="2" t="inlineStr">
@@ -15493,7 +15505,7 @@
       </c>
       <c r="M201" s="2" t="inlineStr">
         <is>
-          <t>genetique_mhoccur</t>
+          <t>vih_mhoccur</t>
         </is>
       </c>
       <c r="N201" s="22" t="inlineStr">
@@ -15510,58 +15522,58 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>pregnn_rporres</t>
+          <t>hvc_mhoccur</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>pregnn_rporres</t>
+          <t>hvc_mhoccur</t>
         </is>
       </c>
       <c r="D202" s="89" t="inlineStr">
         <is>
-          <t>pregnn_rporres</t>
+          <t>hvc_mhoccur</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>Nombre de grossesses</t>
+          <t>Hépatite virale chronique (occurrence)</t>
         </is>
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
-          <t>Numérique</t>
+          <t>Y/N/U</t>
         </is>
       </c>
       <c r="G202" s="89" t="n">
         <v>0</v>
       </c>
       <c r="H202" s="117" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="I202" s="2" t="inlineStr">
         <is>
-          <t>Number of pregnancies : reproductive history variable relevant for women patients; pregnancy/postpartum exposure modulates mood-disorder phenotypes.</t>
+          <t>Chronic viral hepatitis : modifies hepatic drug metabolism; HCV and HBV have neuropsychiatric manifestations (depression, cognitive disturbance) including from interferon-based therapy.</t>
         </is>
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int8 binary</t>
         </is>
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>[see Codage]</t>
+          <t>{0=No/Non, 1=Yes/Oui, NA=Unknown}</t>
         </is>
       </c>
       <c r="L202" s="5" t="inlineStr">
         <is>
-          <t>READY — Comparable construct in all 3 cohorts and data present in all 3 CSVs</t>
+          <t>NOT USABLE — near-zero-variance medical-history flag (minority &lt;5%); no modelling signal</t>
         </is>
       </c>
       <c r="M202" s="2" t="inlineStr">
         <is>
-          <t>pregnn_rporres</t>
+          <t>hvc_mhoccur</t>
         </is>
       </c>
       <c r="N202" s="22" t="inlineStr">
@@ -15578,27 +15590,27 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>menostat_rporres</t>
+          <t>genetique_mhoccur</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>menostat_rporres</t>
+          <t>genetique_mhoccur</t>
         </is>
       </c>
       <c r="D203" s="89" t="inlineStr">
         <is>
-          <t>menostat_rporres</t>
+          <t>genetique_mhoccur</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>Statut ménopausique</t>
+          <t>Maladie génétique (occurrence)</t>
         </is>
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
-          <t>Y/N (ménopausée oui/non)</t>
+          <t>Y/N/U</t>
         </is>
       </c>
       <c r="G203" s="89" t="n">
@@ -15609,7 +15621,7 @@
       </c>
       <c r="I203" s="2" t="inlineStr">
         <is>
-          <t>Menopausal status : hormonal transition with documented effects on mood, cognition, and antidepressant response in women; key reproductive-endocrine variable.</t>
+          <t>Genetic disease : flags syndromic patients (e.g., 22q11.2 deletion, fragile X, Huntington) whose psychiatric presentation is part of a known syndrome — important to stratify in clustering.</t>
         </is>
       </c>
       <c r="J203" s="2" t="inlineStr">
@@ -15624,12 +15636,12 @@
       </c>
       <c r="L203" s="5" t="inlineStr">
         <is>
-          <t>READY — Comparable construct in all 3 cohorts and data present in all 3 CSVs</t>
+          <t>NOT USABLE — near-zero-variance medical-history flag (minority &lt;5%); no modelling signal</t>
         </is>
       </c>
       <c r="M203" s="2" t="inlineStr">
         <is>
-          <t>menostat_rporres</t>
+          <t>genetique_mhoccur</t>
         </is>
       </c>
       <c r="N203" s="22" t="inlineStr">
@@ -15646,48 +15658,48 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>hormonal_rporres</t>
+          <t>pregnn_rporres</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>hormonal_rporres</t>
+          <t>pregnn_rporres</t>
         </is>
       </c>
       <c r="D204" s="89" t="inlineStr">
         <is>
-          <t>hormonal_rporres</t>
+          <t>pregnn_rporres</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>Traitement hormonal en cours</t>
+          <t>Nombre de grossesses</t>
         </is>
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>Y/N</t>
+          <t>Numérique</t>
         </is>
       </c>
       <c r="G204" s="89" t="n">
         <v>0</v>
       </c>
       <c r="H204" s="117" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="I204" s="2" t="inlineStr">
         <is>
-          <t>Hormonal treatment (contraception, HRT) : modifies mood, psychotropic pharmacokinetics, and clinical course; important covariate for clustering of women patients.</t>
+          <t>Number of pregnancies : reproductive history variable relevant for women patients; pregnancy/postpartum exposure modulates mood-disorder phenotypes.</t>
         </is>
       </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>int8 binary</t>
+          <t>float</t>
         </is>
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>{0=No/Non, 1=Yes/Oui, NA=Unknown}</t>
+          <t>[see Codage]</t>
         </is>
       </c>
       <c r="L204" s="5" t="inlineStr">
@@ -15697,7 +15709,7 @@
       </c>
       <c r="M204" s="2" t="inlineStr">
         <is>
-          <t>hormonal_rporres</t>
+          <t>pregnn_rporres</t>
         </is>
       </c>
       <c r="N204" s="22" t="inlineStr">
@@ -15714,27 +15726,27 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>mere_structure</t>
+          <t>menostat_rporres</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>mere_structure</t>
+          <t>menostat_rporres</t>
         </is>
       </c>
       <c r="D205" s="89" t="inlineStr">
         <is>
-          <t>mere_structure</t>
+          <t>menostat_rporres</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>Mère — présence d'un trouble psychiatrique</t>
+          <t>Statut ménopausique</t>
         </is>
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
-          <t>Y/N/U (BP/SZ) ; 0=Non/1=Oui/2=NSP (DR) — la mère présente-t-elle un trouble psychiatrique</t>
+          <t>Y/N (ménopausée oui/non)</t>
         </is>
       </c>
       <c r="G205" s="89" t="n">
@@ -15745,7 +15757,7 @@
       </c>
       <c r="I205" s="2" t="inlineStr">
         <is>
-          <t>Maternal psychiatric/composite history : marker of vertical familial risk. NOTE construct mismatch: BP/SZ ask about composite presence (psy OR substance OR suicide OR cardio); DR asks specifically about psychiatric antecedents. Harmonization needed before clustering.</t>
+          <t>Menopausal status : hormonal transition with documented effects on mood, cognition, and antidepressant response in women; key reproductive-endocrine variable.</t>
         </is>
       </c>
       <c r="J205" s="2" t="inlineStr">
@@ -15765,7 +15777,7 @@
       </c>
       <c r="M205" s="2" t="inlineStr">
         <is>
-          <t>mere_structure</t>
+          <t>menostat_rporres</t>
         </is>
       </c>
       <c r="N205" s="22" t="inlineStr">
@@ -15773,67 +15785,57 @@
           <t>3 (BP/SZ/DR)</t>
         </is>
       </c>
-      <c r="O205" t="inlineStr">
-        <is>
-          <t>Recode: BP/SZ {Y→1, N→0, U→NA}; DR {0→0, 1→1, 2→NA}. Pool as Y/N indicator of maternal family history.</t>
-        </is>
-      </c>
-      <c r="P205" t="inlineStr">
-        <is>
-          <t>Comparable across cohorts: thesauri confirm 'parent psychiatric disorder Y/N' in all 3. Encode Oui-&gt;1/Non-&gt;0/NSP-&gt;NaN. v2 'composite' label was incorrect.</t>
-        </is>
-      </c>
     </row>
     <row r="206" ht="21" customFormat="1" customHeight="1" s="13">
-      <c r="A206" s="72" t="inlineStr">
+      <c r="A206" s="2" t="inlineStr">
         <is>
           <t>ANTECEDENTS</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>mere_suicide</t>
+          <t>hormonal_rporres</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>mere_suicide</t>
+          <t>hormonal_rporres</t>
         </is>
       </c>
       <c r="D206" s="89" t="inlineStr">
         <is>
-          <t>mere_suicide</t>
+          <t>hormonal_rporres</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>Mère — antécédent de suicide / tentative (ordinal)</t>
+          <t>Traitement hormonal en cours</t>
         </is>
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
-          <t>Aucun/Tentative de suicide/Suicide abouti/NSP (BP/SZ) ; 0/1/2/3 (DR)</t>
+          <t>Y/N</t>
         </is>
       </c>
       <c r="G206" s="89" t="n">
         <v>0</v>
       </c>
       <c r="H206" s="117" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I206" s="2" t="inlineStr">
         <is>
-          <t>Maternal suicide history : strong family-aggregation suicide risk variable; trans-diagnostic clustering on suicide-risk subtypes is well established.</t>
+          <t>Hormonal treatment (contraception, HRT) : modifies mood, psychotropic pharmacokinetics, and clinical course; important covariate for clustering of women patients.</t>
         </is>
       </c>
       <c r="J206" s="2" t="inlineStr">
         <is>
-          <t>int8 categorical</t>
+          <t>int8 binary</t>
         </is>
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>{0, 1, 2, 3}</t>
+          <t>{0=No/Non, 1=Yes/Oui, NA=Unknown}</t>
         </is>
       </c>
       <c r="L206" s="5" t="inlineStr">
@@ -15843,22 +15845,12 @@
       </c>
       <c r="M206" s="2" t="inlineStr">
         <is>
-          <t>mere_suicide</t>
+          <t>hormonal_rporres</t>
         </is>
       </c>
       <c r="N206" s="22" t="inlineStr">
         <is>
           <t>3 (BP/SZ/DR)</t>
-        </is>
-      </c>
-      <c r="O206" t="inlineStr">
-        <is>
-          <t>Build a manual mapping table per row aligning the categories. Most cases are simple ID renumbering (1-N vs 0-(N-1)).</t>
-        </is>
-      </c>
-      <c r="P206" t="inlineStr">
-        <is>
-          <t>Comparable as ordinal across cohorts. Encode Aucun-&gt;0, Tentative-&gt;1, Suicide abouti-&gt;2, NSP-&gt;NaN. Bound [0,2].</t>
         </is>
       </c>
     </row>
@@ -15870,27 +15862,27 @@
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>pere_structure</t>
+          <t>mere_structure</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>pere_structure</t>
+          <t>mere_structure</t>
         </is>
       </c>
       <c r="D207" s="89" t="inlineStr">
         <is>
-          <t>pere_structure</t>
+          <t>mere_structure</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>Père — présence d'un trouble psychiatrique</t>
+          <t>Mère — présence d'un trouble psychiatrique</t>
         </is>
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
-          <t>Y/N/U (BP/SZ) ; 0=Non/1=Oui/2=NSP (DR) — le père présente-t-il un trouble psychiatrique</t>
+          <t>Y/N/U (BP/SZ) ; 0=Non/1=Oui/2=NSP (DR) — la mère présente-t-elle un trouble psychiatrique</t>
         </is>
       </c>
       <c r="G207" s="89" t="n">
@@ -15901,271 +15893,271 @@
       </c>
       <c r="I207" s="2" t="inlineStr">
         <is>
+          <t>Maternal psychiatric/composite history : marker of vertical familial risk. NOTE construct mismatch: BP/SZ ask about composite presence (psy OR substance OR suicide OR cardio); DR asks specifically about psychiatric antecedents. Harmonization needed before clustering.</t>
+        </is>
+      </c>
+      <c r="J207" s="2" t="inlineStr">
+        <is>
+          <t>int8 binary</t>
+        </is>
+      </c>
+      <c r="K207" s="2" t="inlineStr">
+        <is>
+          <t>{0=No/Non, 1=Yes/Oui, NA=Unknown}</t>
+        </is>
+      </c>
+      <c r="L207" s="5" t="inlineStr">
+        <is>
+          <t>READY — Comparable construct in all 3 cohorts and data present in all 3 CSVs</t>
+        </is>
+      </c>
+      <c r="M207" s="2" t="inlineStr">
+        <is>
+          <t>mere_structure</t>
+        </is>
+      </c>
+      <c r="N207" s="22" t="inlineStr">
+        <is>
+          <t>3 (BP/SZ/DR)</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>Recode: BP/SZ {Y→1, N→0, U→NA}; DR {0→0, 1→1, 2→NA}. Pool as Y/N indicator of maternal family history.</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>Comparable across cohorts: thesauri confirm 'parent psychiatric disorder Y/N' in all 3. Encode Oui-&gt;1/Non-&gt;0/NSP-&gt;NaN. v2 'composite' label was incorrect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="21" customFormat="1" customHeight="1" s="13">
+      <c r="A208" s="72" t="inlineStr">
+        <is>
+          <t>ANTECEDENTS</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>mere_suicide</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>mere_suicide</t>
+        </is>
+      </c>
+      <c r="D208" s="89" t="inlineStr">
+        <is>
+          <t>mere_suicide</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>Mère — antécédent de suicide / tentative (ordinal)</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>Aucun/Tentative de suicide/Suicide abouti/NSP (BP/SZ) ; 0/1/2/3 (DR)</t>
+        </is>
+      </c>
+      <c r="G208" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="H208" s="117" t="n">
+        <v>2</v>
+      </c>
+      <c r="I208" s="2" t="inlineStr">
+        <is>
+          <t>Maternal suicide history : strong family-aggregation suicide risk variable; trans-diagnostic clustering on suicide-risk subtypes is well established.</t>
+        </is>
+      </c>
+      <c r="J208" s="2" t="inlineStr">
+        <is>
+          <t>int8 categorical</t>
+        </is>
+      </c>
+      <c r="K208" s="2" t="inlineStr">
+        <is>
+          <t>{0, 1, 2, 3}</t>
+        </is>
+      </c>
+      <c r="L208" s="5" t="inlineStr">
+        <is>
+          <t>READY — Comparable construct in all 3 cohorts and data present in all 3 CSVs</t>
+        </is>
+      </c>
+      <c r="M208" s="2" t="inlineStr">
+        <is>
+          <t>mere_suicide</t>
+        </is>
+      </c>
+      <c r="N208" s="22" t="inlineStr">
+        <is>
+          <t>3 (BP/SZ/DR)</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>Build a manual mapping table per row aligning the categories. Most cases are simple ID renumbering (1-N vs 0-(N-1)).</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>Comparable as ordinal across cohorts. Encode Aucun-&gt;0, Tentative-&gt;1, Suicide abouti-&gt;2, NSP-&gt;NaN. Bound [0,2].</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="21" customFormat="1" customHeight="1" s="13">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>ANTECEDENTS</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>pere_structure</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>pere_structure</t>
+        </is>
+      </c>
+      <c r="D209" s="89" t="inlineStr">
+        <is>
+          <t>pere_structure</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>Père — présence d'un trouble psychiatrique</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>Y/N/U (BP/SZ) ; 0=Non/1=Oui/2=NSP (DR) — le père présente-t-il un trouble psychiatrique</t>
+        </is>
+      </c>
+      <c r="G209" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="H209" s="117" t="n">
+        <v>1</v>
+      </c>
+      <c r="I209" s="2" t="inlineStr">
+        <is>
           <t>Paternal psychiatric/composite history : marker of vertical familial risk. Same construct mismatch as `mere_structure`.</t>
         </is>
       </c>
-      <c r="J207" s="2" t="inlineStr">
+      <c r="J209" s="2" t="inlineStr">
         <is>
           <t>int8 binary</t>
         </is>
       </c>
-      <c r="K207" s="2" t="inlineStr">
+      <c r="K209" s="2" t="inlineStr">
         <is>
           <t>{0=No/Non, 1=Yes/Oui, NA=Unknown}</t>
         </is>
       </c>
-      <c r="L207" s="5" t="inlineStr">
+      <c r="L209" s="5" t="inlineStr">
         <is>
           <t>READY — Comparable construct in all 3 cohorts and data present in all 3 CSVs</t>
         </is>
       </c>
-      <c r="M207" s="2" t="inlineStr">
+      <c r="M209" s="2" t="inlineStr">
         <is>
           <t>pere_structure</t>
         </is>
       </c>
-      <c r="N207" s="22" t="inlineStr">
+      <c r="N209" s="22" t="inlineStr">
         <is>
           <t>3 (BP/SZ/DR)</t>
         </is>
       </c>
-      <c r="O207" t="inlineStr">
+      <c r="O209" t="inlineStr">
         <is>
           <t>Same recoding as R471. Pool as Y/N indicator of paternal family history.</t>
         </is>
       </c>
-      <c r="P207" t="inlineStr">
+      <c r="P209" t="inlineStr">
         <is>
           <t>Comparable across cohorts: thesauri confirm 'parent psychiatric disorder Y/N' in all 3. Encode Oui-&gt;1/Non-&gt;0/NSP-&gt;NaN. v2 'composite' label was incorrect.</t>
         </is>
       </c>
     </row>
-    <row r="208" ht="21" customFormat="1" customHeight="1" s="13">
-      <c r="A208" s="6" t="inlineStr">
+    <row r="210" ht="21" customFormat="1" customHeight="1" s="13">
+      <c r="A210" s="6" t="inlineStr">
         <is>
           <t>ANTECEDENTS</t>
         </is>
       </c>
-      <c r="B208" s="6" t="inlineStr">
+      <c r="B210" s="6" t="inlineStr">
         <is>
           <t>pere_suicide</t>
         </is>
       </c>
-      <c r="C208" s="6" t="inlineStr">
+      <c r="C210" s="6" t="inlineStr">
         <is>
           <t>pere_suicide</t>
         </is>
       </c>
-      <c r="D208" s="91" t="inlineStr">
+      <c r="D210" s="91" t="inlineStr">
         <is>
           <t>pere_suicide</t>
         </is>
       </c>
-      <c r="E208" s="6" t="inlineStr">
+      <c r="E210" s="6" t="inlineStr">
         <is>
           <t>Père — antécédent de suicide / tentative (ordinal)</t>
         </is>
       </c>
-      <c r="F208" s="6" t="inlineStr">
+      <c r="F210" s="6" t="inlineStr">
         <is>
           <t>Aucun/Tentative de suicide/Suicide abouti/NSP (BP/SZ) ; 0/1/2/3 (DR)</t>
         </is>
       </c>
-      <c r="G208" s="91" t="n">
+      <c r="G210" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="H208" s="118" t="n">
+      <c r="H210" s="118" t="n">
         <v>2</v>
       </c>
-      <c r="I208" s="6" t="inlineStr">
+      <c r="I210" s="6" t="inlineStr">
         <is>
           <t>Paternal suicide history : same rationale as `mere_suicide`.</t>
         </is>
       </c>
-      <c r="J208" s="6" t="inlineStr">
+      <c r="J210" s="6" t="inlineStr">
         <is>
           <t>int8 categorical</t>
         </is>
       </c>
-      <c r="K208" s="6" t="inlineStr">
+      <c r="K210" s="6" t="inlineStr">
         <is>
           <t>{0, 1, 2, 3}</t>
         </is>
       </c>
-      <c r="L208" s="7" t="inlineStr">
+      <c r="L210" s="7" t="inlineStr">
         <is>
           <t>READY — Comparable construct in all 3 cohorts and data present in all 3 CSVs</t>
         </is>
       </c>
-      <c r="M208" s="6" t="inlineStr">
+      <c r="M210" s="6" t="inlineStr">
         <is>
           <t>pere_suicide</t>
         </is>
       </c>
-      <c r="N208" s="22" t="inlineStr">
+      <c r="N210" s="22" t="inlineStr">
         <is>
           <t>3 (BP/SZ/DR)</t>
         </is>
       </c>
-      <c r="P208" t="inlineStr">
+      <c r="P210" t="inlineStr">
         <is>
           <t>Comparable as ordinal across cohorts. Encode Aucun-&gt;0, Tentative-&gt;1, Suicide abouti-&gt;2, NSP-&gt;NaN. Bound [0,2].</t>
-        </is>
-      </c>
-    </row>
-    <row r="209" ht="21" customFormat="1" customHeight="1" s="13">
-      <c r="A209" s="73" t="inlineStr">
-        <is>
-          <t>SOIN SUIVI HOSP ARRET TRAVAIL</t>
-        </is>
-      </c>
-      <c r="B209" s="74" t="inlineStr">
-        <is>
-          <t>agedebut_hospitalisation</t>
-        </is>
-      </c>
-      <c r="C209" s="74" t="inlineStr">
-        <is>
-          <t>agedebut_hospitalisation_first</t>
-        </is>
-      </c>
-      <c r="D209" s="105" t="inlineStr">
-        <is>
-          <t>agedebut_hospitalisation_lt</t>
-        </is>
-      </c>
-      <c r="E209" s="74" t="inlineStr">
-        <is>
-          <t>Âge à la première hospitalisation psychiatrique</t>
-        </is>
-      </c>
-      <c r="F209" s="74" t="inlineStr">
-        <is>
-          <t>Numérique (années) ; codes diffèrent : BP=non-suffixé, SZ=`_FIRST` (libellé : 'pour trouble psychotique'), DR=`_LT`</t>
-        </is>
-      </c>
-      <c r="G209" s="105" t="n">
-        <v>5</v>
-      </c>
-      <c r="H209" s="134" t="n">
-        <v>90</v>
-      </c>
-      <c r="I209" s="74" t="inlineStr">
-        <is>
-          <t>Age at first psychiatric hospitalization : a strong illness-onset/severity marker. The first hospitalization typically marks a clinically severe escalation; early first hospitalization is a robust predictor of more severe trajectory across all three pathologies. NOTE: SZ specifically codes the first PSYCHOTIC hospitalisation, while BP/DR code the first hospitalisation regardless of episode type — verify per source before pooling.</t>
-        </is>
-      </c>
-      <c r="J209" s="74" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="K209" s="74" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="L209" s="75" t="inlineStr">
-        <is>
-          <t>READY — Comparable construct in all 3 cohorts and data present in all 3 CSVs</t>
-        </is>
-      </c>
-      <c r="M209" s="76" t="inlineStr">
-        <is>
-          <t>agedebut_hospitalisation</t>
-        </is>
-      </c>
-      <c r="N209" s="22" t="inlineStr">
-        <is>
-          <t>3 (BP/SZ/DR)</t>
-        </is>
-      </c>
-      <c r="O209" t="inlineStr">
-        <is>
-          <t>POOL as 'age at first psychiatric hospitalization' (years). Same per-cohort semantic note as R423.</t>
-        </is>
-      </c>
-      <c r="P209" t="inlineStr">
-        <is>
-          <t>✓ COMPARABLE per data. BP any-cause median=27 (n=3713), SZ psychotic-only median=22 (n=1729), DR any-cause median=39 (n=245). SZ patients hospitalized younger (consistent with first-episode psychosis); DR later (consistent with late-onset depression). Same biological construct: age at first psychiatric hospitalization.</t>
-        </is>
-      </c>
-    </row>
-    <row r="210" ht="21" customFormat="1" customHeight="1" s="13">
-      <c r="A210" s="73" t="inlineStr">
-        <is>
-          <t>SOIN SUIVI HOSP ARRET TRAVAIL</t>
-        </is>
-      </c>
-      <c r="B210" s="74" t="inlineStr">
-        <is>
-          <t>nboccur_hospitalisation</t>
-        </is>
-      </c>
-      <c r="C210" s="74" t="inlineStr">
-        <is>
-          <t>nboccur_hospitalisation_lt</t>
-        </is>
-      </c>
-      <c r="D210" s="105" t="inlineStr">
-        <is>
-          <t>nboccur_hospitalisation_lt</t>
-        </is>
-      </c>
-      <c r="E210" s="74" t="inlineStr">
-        <is>
-          <t>Nombre total d'hospitalisations psychiatriques (vie entière)</t>
-        </is>
-      </c>
-      <c r="F210" s="74" t="inlineStr">
-        <is>
-          <t>Numérique ; BP non-suffixé, SZ+DR ont le suffixe `_LT`</t>
-        </is>
-      </c>
-      <c r="G210" s="105" t="n">
-        <v>0</v>
-      </c>
-      <c r="H210" s="134" t="n">
-        <v>100</v>
-      </c>
-      <c r="I210" s="74" t="inlineStr">
-        <is>
-          <t>Lifetime number of psychiatric hospitalisations : direct severity-of-illness index; one of the most cluster-relevant variables in care-utilization phenotyping. High repeated-hospitalisation phenotype distinguishes severe from milder trajectories.</t>
-        </is>
-      </c>
-      <c r="J210" s="74" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="K210" s="74" t="inlineStr">
-        <is>
-          <t>mmHg</t>
-        </is>
-      </c>
-      <c r="L210" s="75" t="inlineStr">
-        <is>
-          <t>READY — Comparable construct in all 3 cohorts and data present in all 3 CSVs</t>
-        </is>
-      </c>
-      <c r="M210" s="74" t="inlineStr">
-        <is>
-          <t>nboccur_hospitalisation_lt</t>
-        </is>
-      </c>
-      <c r="N210" s="22" t="inlineStr">
-        <is>
-          <t>3 (BP/SZ/DR)</t>
-        </is>
-      </c>
-      <c r="O210" t="inlineStr">
-        <is>
-          <t>Verify units in label (years, months, weeks, days, count). Convert if different across pathologies.</t>
-        </is>
-      </c>
-      <c r="P210" t="inlineStr">
-        <is>
-          <t>Numeric variable with explicit 'NUM' codage in source.</t>
         </is>
       </c>
     </row>
@@ -16177,38 +16169,38 @@
       </c>
       <c r="B211" s="74" t="inlineStr">
         <is>
-          <t>hodur_hospitalisation</t>
+          <t>agedebut_hospitalisation</t>
         </is>
       </c>
       <c r="C211" s="74" t="inlineStr">
         <is>
-          <t>hodur_hospitalisation_lt</t>
+          <t>agedebut_hospitalisation_first</t>
         </is>
       </c>
       <c r="D211" s="105" t="inlineStr">
         <is>
-          <t>hodur_hospitalisation_lt</t>
+          <t>agedebut_hospitalisation_lt</t>
         </is>
       </c>
       <c r="E211" s="74" t="inlineStr">
         <is>
-          <t>Durée totale des hospitalisations psychiatriques (vie entière, mois)</t>
+          <t>Âge à la première hospitalisation psychiatrique</t>
         </is>
       </c>
       <c r="F211" s="74" t="inlineStr">
         <is>
-          <t>Numérique (mois) ; BP non-suffixé, SZ+DR ont le suffixe `_LT`</t>
+          <t>Numérique (années) ; codes diffèrent : BP=non-suffixé, SZ=`_FIRST` (libellé : 'pour trouble psychotique'), DR=`_LT`</t>
         </is>
       </c>
       <c r="G211" s="105" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H211" s="134" t="n">
-        <v>600</v>
+        <v>90</v>
       </c>
       <c r="I211" s="74" t="inlineStr">
         <is>
-          <t>Lifetime cumulative duration of psychiatric hospitalisations : key severity index complementing count; long cumulative stays mark chronic-course phenotypes. Together with NBOCCUR, allows derivation of mean stay duration.</t>
+          <t>Age at first psychiatric hospitalization : a strong illness-onset/severity marker. The first hospitalization typically marks a clinically severe escalation; early first hospitalization is a robust predictor of more severe trajectory across all three pathologies. NOTE: SZ specifically codes the first PSYCHOTIC hospitalisation, while BP/DR code the first hospitalisation regardless of episode type — verify per source before pooling.</t>
         </is>
       </c>
       <c r="J211" s="74" t="inlineStr">
@@ -16218,7 +16210,7 @@
       </c>
       <c r="K211" s="74" t="inlineStr">
         <is>
-          <t>months</t>
+          <t>years</t>
         </is>
       </c>
       <c r="L211" s="75" t="inlineStr">
@@ -16226,9 +16218,9 @@
           <t>READY — Comparable construct in all 3 cohorts and data present in all 3 CSVs</t>
         </is>
       </c>
-      <c r="M211" s="74" t="inlineStr">
-        <is>
-          <t>hodur_hospitalisation_lt</t>
+      <c r="M211" s="76" t="inlineStr">
+        <is>
+          <t>agedebut_hospitalisation</t>
         </is>
       </c>
       <c r="N211" s="22" t="inlineStr">
@@ -16238,607 +16230,627 @@
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>Verify units: mmHg for BP, msec for QT/QTc, bpm for HR, kg for weight, cm for height. Convert if any source uses different.</t>
+          <t>POOL as 'age at first psychiatric hospitalization' (years). Same per-cohort semantic note as R423.</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Clinical numeric measurement (HR, BP, weight, height, etc.).</t>
+          <t>✓ COMPARABLE per data. BP any-cause median=27 (n=3713), SZ psychotic-only median=22 (n=1729), DR any-cause median=39 (n=245). SZ patients hospitalized younger (consistent with first-episode psychosis); DR later (consistent with late-onset depression). Same biological construct: age at first psychiatric hospitalization.</t>
         </is>
       </c>
     </row>
     <row r="212" ht="21" customFormat="1" customHeight="1" s="13">
-      <c r="A212" s="77" t="inlineStr">
+      <c r="A212" s="73" t="inlineStr">
         <is>
           <t>SOIN SUIVI HOSP ARRET TRAVAIL</t>
         </is>
       </c>
       <c r="B212" s="74" t="inlineStr">
         <is>
-          <t>hooccur_arret_travail_actuel</t>
+          <t>nboccur_hospitalisation</t>
         </is>
       </c>
       <c r="C212" s="74" t="inlineStr">
         <is>
-          <t>hooccur_arret_travail_actuel</t>
+          <t>nboccur_hospitalisation_lt</t>
         </is>
       </c>
       <c r="D212" s="105" t="inlineStr">
         <is>
-          <t>hooccur_arret_travail_actuel</t>
+          <t>nboccur_hospitalisation_lt</t>
         </is>
       </c>
       <c r="E212" s="74" t="inlineStr">
         <is>
-          <t>Le patient est-il actuellement en arrêt de travail ?</t>
+          <t>Nombre total d'hospitalisations psychiatriques (vie entière)</t>
         </is>
       </c>
       <c r="F212" s="74" t="inlineStr">
         <is>
-          <t>Y/N (BP/SZ) ; Y/N/NA (DR) — verbatim Tier A</t>
+          <t>Numérique ; BP non-suffixé, SZ+DR ont le suffixe `_LT`</t>
         </is>
       </c>
       <c r="G212" s="105" t="n">
         <v>0</v>
       </c>
       <c r="H212" s="134" t="n">
+        <v>100</v>
+      </c>
+      <c r="I212" s="74" t="inlineStr">
+        <is>
+          <t>Lifetime number of psychiatric hospitalisations : direct severity-of-illness index; one of the most cluster-relevant variables in care-utilization phenotyping. High repeated-hospitalisation phenotype distinguishes severe from milder trajectories.</t>
+        </is>
+      </c>
+      <c r="J212" s="74" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="K212" s="74" t="inlineStr">
+        <is>
+          <t>mmHg</t>
+        </is>
+      </c>
+      <c r="L212" s="75" t="inlineStr">
+        <is>
+          <t>READY — Comparable construct in all 3 cohorts and data present in all 3 CSVs</t>
+        </is>
+      </c>
+      <c r="M212" s="74" t="inlineStr">
+        <is>
+          <t>nboccur_hospitalisation_lt</t>
+        </is>
+      </c>
+      <c r="N212" s="22" t="inlineStr">
+        <is>
+          <t>3 (BP/SZ/DR)</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>Verify units in label (years, months, weeks, days, count). Convert if different across pathologies.</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>Numeric variable with explicit 'NUM' codage in source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="21" customFormat="1" customHeight="1" s="13">
+      <c r="A213" s="73" t="inlineStr">
+        <is>
+          <t>SOIN SUIVI HOSP ARRET TRAVAIL</t>
+        </is>
+      </c>
+      <c r="B213" s="74" t="inlineStr">
+        <is>
+          <t>hodur_hospitalisation</t>
+        </is>
+      </c>
+      <c r="C213" s="74" t="inlineStr">
+        <is>
+          <t>hodur_hospitalisation_lt</t>
+        </is>
+      </c>
+      <c r="D213" s="105" t="inlineStr">
+        <is>
+          <t>hodur_hospitalisation_lt</t>
+        </is>
+      </c>
+      <c r="E213" s="74" t="inlineStr">
+        <is>
+          <t>Durée totale des hospitalisations psychiatriques (vie entière, mois)</t>
+        </is>
+      </c>
+      <c r="F213" s="74" t="inlineStr">
+        <is>
+          <t>Numérique (mois) ; BP non-suffixé, SZ+DR ont le suffixe `_LT`</t>
+        </is>
+      </c>
+      <c r="G213" s="105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H213" s="134" t="n">
+        <v>600</v>
+      </c>
+      <c r="I213" s="74" t="inlineStr">
+        <is>
+          <t>Lifetime cumulative duration of psychiatric hospitalisations : key severity index complementing count; long cumulative stays mark chronic-course phenotypes. Together with NBOCCUR, allows derivation of mean stay duration.</t>
+        </is>
+      </c>
+      <c r="J213" s="74" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="K213" s="74" t="inlineStr">
+        <is>
+          <t>months</t>
+        </is>
+      </c>
+      <c r="L213" s="75" t="inlineStr">
+        <is>
+          <t>READY — Comparable construct in all 3 cohorts and data present in all 3 CSVs</t>
+        </is>
+      </c>
+      <c r="M213" s="74" t="inlineStr">
+        <is>
+          <t>hodur_hospitalisation_lt</t>
+        </is>
+      </c>
+      <c r="N213" s="22" t="inlineStr">
+        <is>
+          <t>3 (BP/SZ/DR)</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>Verify units: mmHg for BP, msec for QT/QTc, bpm for HR, kg for weight, cm for height. Convert if any source uses different.</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>Clinical numeric measurement (HR, BP, weight, height, etc.).</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="21" customFormat="1" customHeight="1" s="13">
+      <c r="A214" s="77" t="inlineStr">
+        <is>
+          <t>SOIN SUIVI HOSP ARRET TRAVAIL</t>
+        </is>
+      </c>
+      <c r="B214" s="74" t="inlineStr">
+        <is>
+          <t>hooccur_arret_travail_actuel</t>
+        </is>
+      </c>
+      <c r="C214" s="74" t="inlineStr">
+        <is>
+          <t>hooccur_arret_travail_actuel</t>
+        </is>
+      </c>
+      <c r="D214" s="105" t="inlineStr">
+        <is>
+          <t>hooccur_arret_travail_actuel</t>
+        </is>
+      </c>
+      <c r="E214" s="74" t="inlineStr">
+        <is>
+          <t>Le patient est-il actuellement en arrêt de travail ?</t>
+        </is>
+      </c>
+      <c r="F214" s="74" t="inlineStr">
+        <is>
+          <t>Y/N (BP/SZ) ; Y/N/NA (DR) — verbatim Tier A</t>
+        </is>
+      </c>
+      <c r="G214" s="105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H214" s="134" t="n">
         <v>1</v>
       </c>
-      <c r="I212" s="74" t="inlineStr">
+      <c r="I214" s="74" t="inlineStr">
         <is>
           <t>Current work disability status : core functional outcome variable. Concurrent sick leave is a marker of acute functional impairment and a strong predictor of recovery trajectory; widely used in psychiatric outcome studies.</t>
         </is>
       </c>
-      <c r="J212" s="74" t="inlineStr">
+      <c r="J214" s="74" t="inlineStr">
         <is>
           <t>int8 binary</t>
         </is>
       </c>
-      <c r="K212" s="74" t="inlineStr">
+      <c r="K214" s="74" t="inlineStr">
         <is>
           <t>{0=No/Non, 1=Yes/Oui, NA=Unknown}</t>
         </is>
       </c>
-      <c r="L212" s="75" t="inlineStr">
+      <c r="L214" s="75" t="inlineStr">
         <is>
           <t>READY — Comparable construct in all 3 cohorts and data present in all 3 CSVs</t>
         </is>
       </c>
-      <c r="M212" s="74" t="inlineStr">
+      <c r="M214" s="74" t="inlineStr">
         <is>
           <t>hooccur_arret_travail_actuel</t>
         </is>
       </c>
-      <c r="N212" s="22" t="inlineStr">
+      <c r="N214" s="22" t="inlineStr">
         <is>
           <t>3 (BP/SZ/DR)</t>
         </is>
       </c>
-      <c r="O212" t="inlineStr">
+      <c r="O214" t="inlineStr">
         <is>
           <t>Recode all to {1=Yes, 0=No, NA=Unknown/Not-applicable}. Distinguish 'patient not working' (NA) from 'patient working, no sick leave' (0). For SZ/DR the NA encoding is explicit; for BP, U=Unknown is a different semantic and may need a separate NA category.</t>
         </is>
       </c>
-      <c r="P212" t="inlineStr">
+      <c r="P214" t="inlineStr">
         <is>
           <t>Encode Oui-&gt;1/Non-&gt;0; 'Non applicable'/NA (not in workforce) -&gt; NaN (NOT 0). DR codes 0/1/2 (2=NA-&gt;NaN). Bound [0,1].</t>
         </is>
       </c>
     </row>
-    <row r="213" ht="21" customFormat="1" customHeight="1" s="13">
-      <c r="A213" s="78" t="inlineStr">
+    <row r="215" ht="21" customFormat="1" customHeight="1" s="13">
+      <c r="A215" s="78" t="inlineStr">
         <is>
           <t>SOIN SUIVI HOSP ARRET TRAVAIL</t>
         </is>
       </c>
-      <c r="B213" s="79" t="inlineStr">
+      <c r="B215" s="79" t="inlineStr">
         <is>
           <t>hodur_arret_travail_actuel</t>
         </is>
       </c>
-      <c r="C213" s="79" t="n"/>
-      <c r="D213" s="106" t="inlineStr">
+      <c r="C215" s="79" t="n"/>
+      <c r="D215" s="106" t="inlineStr">
         <is>
           <t>hodur_arret_travail_actuel</t>
         </is>
       </c>
-      <c r="E213" s="79" t="inlineStr">
+      <c r="E215" s="79" t="inlineStr">
         <is>
           <t>Est-ce un arrêt de travail de longue durée ?</t>
         </is>
       </c>
-      <c r="F213" s="79" t="inlineStr">
+      <c r="F215" s="79" t="inlineStr">
         <is>
           <t>Y/N (BP) ; Y/N (DR libellé '&gt;Longue durée?') ; BP+DR seulement</t>
         </is>
       </c>
-      <c r="G213" s="106" t="n">
+      <c r="G215" s="106" t="n">
         <v>0</v>
       </c>
-      <c r="H213" s="135" t="n">
+      <c r="H215" s="135" t="n">
         <v>1</v>
       </c>
-      <c r="I213" s="79" t="inlineStr">
+      <c r="I215" s="79" t="inlineStr">
         <is>
           <t>Current sick leave is long-duration : marker of severe functional impairment in the acute period. Long-term work disability (&gt;3-6 months) is a strong predictor of chronic-course outcomes and disability pension trajectories.</t>
         </is>
       </c>
-      <c r="J213" s="79" t="inlineStr">
+      <c r="J215" s="79" t="inlineStr">
         <is>
           <t>int8 binary</t>
         </is>
       </c>
-      <c r="K213" s="79" t="inlineStr">
+      <c r="K215" s="79" t="inlineStr">
         <is>
           <t>{0=No/Non, 1=Yes/Oui, NA}</t>
         </is>
       </c>
-      <c r="L213" s="80" t="inlineStr">
+      <c r="L215" s="80" t="inlineStr">
         <is>
           <t>PARTIAL — Comparable in 2 of 3 cohorts (Tier B); usable for 2-cohort joint clustering</t>
         </is>
       </c>
-      <c r="M213" s="79" t="inlineStr">
+      <c r="M215" s="79" t="inlineStr">
         <is>
           <t>hodur_arret_travail_actuel</t>
         </is>
       </c>
-      <c r="N213" s="22" t="inlineStr">
+      <c r="N215" s="22" t="inlineStr">
         <is>
           <t>2 (BP/DR)</t>
         </is>
       </c>
-      <c r="O213" t="inlineStr">
+      <c r="O215" t="inlineStr">
         <is>
           <t>Verify units: mmHg for BP, msec for QT/QTc, bpm for HR, kg for weight, cm for height. Convert if any source uses different.</t>
         </is>
       </c>
-      <c r="P213" t="inlineStr">
+      <c r="P215" t="inlineStr">
         <is>
           <t>Encode Oui-&gt;1/Non-&gt;0; 'Non applicable'/NA (not in workforce) -&gt; NaN (NOT 0). DR codes 0/1/2 (2=NA-&gt;NaN). Bound [0,1].</t>
         </is>
       </c>
     </row>
-    <row r="214" ht="21" customFormat="1" customHeight="1" s="13">
-      <c r="A214" s="84" t="inlineStr">
+    <row r="216" ht="21" customFormat="1" customHeight="1" s="13">
+      <c r="A216" s="84" t="inlineStr">
         <is>
           <t>SOCIAL</t>
         </is>
       </c>
-      <c r="B214" s="82" t="inlineStr">
+      <c r="B216" s="82" t="inlineStr">
         <is>
           <t>edulevel</t>
         </is>
       </c>
-      <c r="C214" s="82" t="inlineStr">
+      <c r="C216" s="82" t="inlineStr">
         <is>
           <t>edulevel</t>
         </is>
       </c>
-      <c r="D214" s="107" t="inlineStr">
+      <c r="D216" s="107" t="inlineStr">
         <is>
           <t>edulevel</t>
         </is>
       </c>
-      <c r="E214" s="82" t="inlineStr">
+      <c r="E216" s="82" t="inlineStr">
         <is>
           <t>Niveau d'éducation (années / dernier grade obtenu)</t>
         </is>
       </c>
-      <c r="F214" s="82" t="inlineStr">
+      <c r="F216" s="82" t="inlineStr">
         <is>
           <t>BP+DR : codage uniforme (CP-CM2=1-5, collège=6-9, lycée=10-12, CAP=13, BEP=14, BAC+1 à BAC+5=15-19, Doctorat=20) ; SZ : TEXTE libre</t>
         </is>
       </c>
-      <c r="G214" s="107" t="n">
+      <c r="G216" s="107" t="n">
         <v>1</v>
       </c>
-      <c r="H214" s="136" t="n">
+      <c r="H216" s="136" t="n">
         <v>20</v>
       </c>
-      <c r="I214" s="82" t="inlineStr">
+      <c r="I216" s="82" t="inlineStr">
         <is>
           <t>Educational attainment : robust predictor of cognitive reserve, premorbid IQ, and socioeconomic stratification; one of the highest-yield single sociodemographic variables for psychiatric clustering. NOTE: SZ stores as free text — needs harmonization to BP/DR's numeric scale before pooling.</t>
         </is>
       </c>
-      <c r="J214" s="82" t="inlineStr">
+      <c r="J216" s="82" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="K214" s="82" t="inlineStr">
+      <c r="K216" s="82" t="inlineStr">
         <is>
           <t>years</t>
         </is>
       </c>
-      <c r="L214" s="83" t="inlineStr">
+      <c r="L216" s="83" t="inlineStr">
         <is>
           <t>READY — Comparable construct in all 3 cohorts and data present in all 3 CSVs</t>
         </is>
       </c>
-      <c r="M214" s="82" t="inlineStr">
+      <c r="M216" s="82" t="inlineStr">
         <is>
           <t>edulevel</t>
         </is>
       </c>
-      <c r="N214" s="22" t="inlineStr">
+      <c r="N216" s="22" t="inlineStr">
         <is>
           <t>3 (BP/SZ/DR)</t>
         </is>
       </c>
-      <c r="O214" t="inlineStr">
+      <c r="O216" t="inlineStr">
         <is>
           <t>Recode both BP and SZ: 'BAC' → 12 (baccalauréat = end of lycée, after 12 years of schooling); other numeric strings → cast to int. Verify other rare strings ('BEP', 'CAP', etc.) per-cohort and apply the thesaurus mapping (CP-CM2=1-5, collège=6-9, lycée=10-12, CAP=13, BEP=14, BAC+1 to BAC+5=15-19, Doctorat=20). DR is ready to pool directly. | Implemented in rules.py::edulevel (SZ text tokens BAC/CAP/Doctorat→ordinal), v2-gated.</t>
         </is>
       </c>
-      <c r="P214" t="inlineStr">
+      <c r="P216" t="inlineStr">
         <is>
           <t>BP/DR uniform ordinal (CP-CM2=1-5...Doctorat=20). SZ is MIXED text/number (~23% numeric, e.g. 'BAC') -&gt; must parse SZ text to the ordinal before use, else SZ unusable. Bound [1,20].</t>
         </is>
       </c>
     </row>
-    <row r="215" ht="21" customFormat="1" customHeight="1" s="13">
-      <c r="A215" s="81" t="inlineStr">
+    <row r="217" ht="21" customFormat="1" customHeight="1" s="13">
+      <c r="A217" s="81" t="inlineStr">
         <is>
           <t>SOCIAL</t>
         </is>
       </c>
-      <c r="B215" s="82" t="inlineStr">
+      <c r="B217" s="82" t="inlineStr">
         <is>
           <t>stprof</t>
         </is>
       </c>
-      <c r="C215" s="82" t="inlineStr">
+      <c r="C217" s="82" t="inlineStr">
         <is>
           <t>stprof</t>
         </is>
       </c>
-      <c r="D215" s="107" t="inlineStr">
+      <c r="D217" s="107" t="inlineStr">
         <is>
           <t>stprof</t>
         </is>
       </c>
-      <c r="E215" s="82" t="inlineStr">
+      <c r="E217" s="82" t="inlineStr">
         <is>
           <t>Statut professionnel actuel</t>
         </is>
       </c>
-      <c r="F215" s="82" t="inlineStr">
+      <c r="F217" s="82" t="inlineStr">
         <is>
           <t>Catégoriel ; BP+DR : 0=sans emploi, 1=actif, 2=retraité, 3=étudiant, 4=pension, 5=au foyer, 6=autres ; SZ : même grille mais 3=étudiant/lycéen, 7=au foyer (réordonné)</t>
         </is>
       </c>
-      <c r="G215" s="107" t="n">
+      <c r="G217" s="107" t="n">
         <v>0</v>
       </c>
-      <c r="H215" s="136" t="n">
+      <c r="H217" s="136" t="n">
         <v>6</v>
       </c>
-      <c r="I215" s="82" t="inlineStr">
+      <c r="I217" s="82" t="inlineStr">
         <is>
           <t>Current occupational status : direct functional outcome measure; differentiates active vs disability-pension vs unemployed phenotypes that have distinct biological and trajectory profiles. NOTE: SZ has slight codage reordering — verify mapping before pooling.</t>
         </is>
       </c>
-      <c r="J215" s="82" t="inlineStr">
+      <c r="J217" s="82" t="inlineStr">
         <is>
           <t>int8 categorical</t>
         </is>
       </c>
-      <c r="K215" s="82" t="inlineStr">
+      <c r="K217" s="82" t="inlineStr">
         <is>
           <t>{0, 1, 2, 4, 5, 6}</t>
         </is>
       </c>
-      <c r="L215" s="83" t="inlineStr">
+      <c r="L217" s="83" t="inlineStr">
         <is>
           <t>READY — Comparable construct in all 3 cohorts and data present in all 3 CSVs</t>
         </is>
       </c>
-      <c r="M215" s="82" t="inlineStr">
+      <c r="M217" s="82" t="inlineStr">
         <is>
           <t>stprof</t>
         </is>
       </c>
-      <c r="N215" s="22" t="inlineStr">
+      <c r="N217" s="22" t="inlineStr">
         <is>
           <t>3 (BP/SZ/DR)</t>
         </is>
       </c>
-      <c r="O215" t="inlineStr">
+      <c r="O217" t="inlineStr">
         <is>
           <t>Pool STPROF raw 0-6 directly across all 3 pathologies. NO recoding needed. Same scheme: {0=sans emploi, 1=actif, 2=retraité, 3=étudiant, 4=pension, 5=au foyer, 6=autres}.</t>
         </is>
       </c>
-      <c r="P215" t="inlineStr">
+      <c r="P217" t="inlineStr">
         <is>
           <t>✓ REVISED: data shows ALL three pathologies use 0-6 numeric scheme. SZ range is 0-6 (not 0-7 as the thesaurus claimed). The thesaurus's '7=Au foyer' for SZ appears to be a documentation error or unused code.</t>
         </is>
       </c>
     </row>
-    <row r="216" ht="21" customFormat="1" customHeight="1" s="13">
-      <c r="A216" s="82" t="inlineStr">
+    <row r="218">
+      <c r="A218" s="82" t="inlineStr">
         <is>
           <t>SOCIAL</t>
         </is>
       </c>
-      <c r="B216" s="82" t="inlineStr">
+      <c r="B218" s="82" t="inlineStr">
         <is>
           <t>jobclas</t>
         </is>
       </c>
-      <c r="C216" s="82" t="inlineStr">
+      <c r="C218" s="82" t="inlineStr">
         <is>
           <t>jobclas</t>
         </is>
       </c>
-      <c r="D216" s="107" t="inlineStr">
+      <c r="D218" s="107" t="inlineStr">
         <is>
           <t>jobclas</t>
         </is>
       </c>
-      <c r="E216" s="82" t="inlineStr">
+      <c r="E218" s="82" t="inlineStr">
         <is>
           <t>Emploi temps plein (Y/N)</t>
         </is>
       </c>
-      <c r="F216" s="82" t="inlineStr">
+      <c r="F218" s="82" t="inlineStr">
         <is>
           <t>Oui/Non (BP/SZ) ; 0/1 (DR) — emploi à temps plein</t>
         </is>
       </c>
-      <c r="G216" s="107" t="n">
+      <c r="G218" s="107" t="n">
         <v>0</v>
       </c>
-      <c r="H216" s="136" t="n">
+      <c r="H218" s="136" t="n">
         <v>1</v>
       </c>
-      <c r="I216" s="82" t="inlineStr">
+      <c r="I218" s="82" t="inlineStr">
         <is>
           <t>Full-time vs part-time employment : finer-grained occupational stratifier; part-time employment is a marker of partial functional recovery / chronic limitation; relevant for occupational-outcome clustering.</t>
         </is>
       </c>
-      <c r="J216" s="82" t="inlineStr">
+      <c r="J218" s="82" t="inlineStr">
         <is>
           <t>int8 binary</t>
         </is>
       </c>
-      <c r="K216" s="82" t="inlineStr">
+      <c r="K218" s="82" t="inlineStr">
         <is>
           <t>{0=No/Non, 1=Yes/Oui, NA}</t>
         </is>
       </c>
-      <c r="L216" s="83" t="inlineStr">
+      <c r="L218" s="83" t="inlineStr">
         <is>
           <t>READY — Comparable construct in all 3 cohorts and data present in all 3 CSVs</t>
         </is>
       </c>
-      <c r="M216" s="82" t="inlineStr">
+      <c r="M218" s="82" t="inlineStr">
         <is>
           <t>jobclas</t>
         </is>
       </c>
-      <c r="N216" s="22" t="inlineStr">
+      <c r="N218" s="22" t="inlineStr">
         <is>
           <t>3 (BP/SZ/DR)</t>
         </is>
       </c>
-      <c r="P216" t="inlineStr">
+      <c r="P218" t="inlineStr">
         <is>
           <t>Encode Oui-&gt;1/Non-&gt;0. Comparable Y/N across all 3 cohorts. Bound [0,1].</t>
         </is>
       </c>
     </row>
-    <row r="217" ht="21" customFormat="1" customHeight="1" s="13">
-      <c r="A217" s="85" t="inlineStr">
+    <row r="219">
+      <c r="A219" s="85" t="inlineStr">
         <is>
           <t>SOCIAL</t>
         </is>
       </c>
-      <c r="B217" s="86" t="inlineStr">
+      <c r="B219" s="86" t="inlineStr">
         <is>
           <t>lvsbjind</t>
         </is>
       </c>
-      <c r="C217" s="86" t="inlineStr">
+      <c r="C219" s="86" t="inlineStr">
         <is>
           <t>vie</t>
         </is>
       </c>
-      <c r="D217" s="108" t="inlineStr">
+      <c r="D219" s="108" t="inlineStr">
         <is>
           <t>lvsbjind</t>
         </is>
       </c>
-      <c r="E217" s="86" t="inlineStr">
+      <c r="E219" s="86" t="inlineStr">
         <is>
           <t>Mode de vie (avec qui le sujet vit / type de logement)</t>
         </is>
       </c>
-      <c r="F217" s="86" t="inlineStr">
+      <c r="F219" s="86" t="inlineStr">
         <is>
           <t>Catégoriel ; codes diffèrent (BP+DR=LVSBJIND, SZ=VIE) ; mêmes catégories 1-8 : seul / chez parents / propre foyer familial / chez enfants / chez famille / colocation / collectivité / autres</t>
         </is>
       </c>
-      <c r="G217" s="108" t="n">
+      <c r="G219" s="108" t="n">
         <v>1</v>
       </c>
-      <c r="H217" s="137" t="n">
+      <c r="H219" s="137" t="n">
         <v>8</v>
       </c>
-      <c r="I217" s="86" t="inlineStr">
+      <c r="I219" s="86" t="inlineStr">
         <is>
           <t>Living arrangement : core social/functional autonomy marker. Living alone vs with parents vs in own family unit vs collective housing differentiates major recovery and dependency phenotypes. Same construct across all three thesauri with same coded categories — only the variable name differs (semantic Tier A). Critical clustering variable for autonomy-trajectory phenotypes.</t>
         </is>
       </c>
-      <c r="J217" s="86" t="inlineStr">
+      <c r="J219" s="86" t="inlineStr">
         <is>
           <t>int8 categorical</t>
         </is>
       </c>
-      <c r="K217" s="86" t="inlineStr">
+      <c r="K219" s="86" t="inlineStr">
         <is>
           <t>{1, 2, 3, 4, 5, 6, 7, 8}</t>
         </is>
       </c>
-      <c r="L217" s="87" t="inlineStr">
+      <c r="L219" s="87" t="inlineStr">
         <is>
           <t>READY — Comparable construct in all 3 cohorts and data present in all 3 CSVs</t>
         </is>
       </c>
-      <c r="M217" s="86" t="inlineStr">
+      <c r="M219" s="86" t="inlineStr">
         <is>
           <t>lvsbjind</t>
         </is>
       </c>
-      <c r="N217" s="22" t="inlineStr">
+      <c r="N219" s="22" t="inlineStr">
         <is>
           <t>3 (BP/SZ/DR)</t>
         </is>
       </c>
-      <c r="O217" t="inlineStr">
+      <c r="O219" t="inlineStr">
         <is>
           <t>Verify SZ data is stored as either text labels OR integers 1-8. If text labels, recode to BP/DR's 1-8 integer convention before pooling. Construct is fully comparable; only the variable name and codage display differ.</t>
         </is>
       </c>
-      <c r="P217" t="inlineStr">
+      <c r="P219" t="inlineStr">
         <is>
           <t>BP/DR numeric codes 1-8; SZ stores TEXT in 'vie' col -&gt; encode SZ text to the 1-8 scheme. Bound [1,8].</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>NEUROPSYCHOLOGIE</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>ivt01_w</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>ivt01_wais4</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>ivt01</t>
-        </is>
-      </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>WAIS IVT processing-speed index</t>
-        </is>
-      </c>
-      <c r="G218" t="n">
-        <v>40</v>
-      </c>
-      <c r="H218" t="n">
-        <v>160</v>
-      </c>
-      <c r="J218" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="K218" t="inlineStr">
-        <is>
-          <t>WAIS processing-speed index (mean 100, SD 15)</t>
-        </is>
-      </c>
-      <c r="L218" t="inlineStr">
-        <is>
-          <t>READY — Comparable in 3 cohorts (Tier A); neuropsy_features.yaml 2026-05-30</t>
-        </is>
-      </c>
-      <c r="M218" t="inlineStr">
-        <is>
-          <t>wais_ivt_index</t>
-        </is>
-      </c>
-      <c r="N218" t="inlineStr">
-        <is>
-          <t>3 (BP/SZ/DR)</t>
-        </is>
-      </c>
-      <c r="O218" t="inlineStr">
-        <is>
-          <t>Index score (100+/-15); present in all 3 cohorts</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>NEUROPSYCHOLOGIE</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>cvlt06_</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>cvlt06_</t>
-        </is>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>CVLT Total Recall, trials 1–5 (verbal learning / acquisition)</t>
-        </is>
-      </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>Numérique (somme des rappels libres, essais 1–5)</t>
-        </is>
-      </c>
-      <c r="G219" t="n">
-        <v>0</v>
-      </c>
-      <c r="H219" t="n">
-        <v>80</v>
-      </c>
-      <c r="I219" t="inlineStr">
-        <is>
-          <t>FEATURE (verbal episodic memory; BP + SZ only — DR has no CVLT). California Verbal Learning Test total free recall summed over the five learning trials — the canonical measure of verbal learning/acquisition. Adds the verbal episodic-memory domain that is otherwise ABSENT from the 3-cohort battery (processing speed, working memory, verbal reasoning, executive shifting — but no memory). Raw count on an identical 16-word/5-trial CVLT in both cohorts (0–80); SZ sits below BP (median 47 vs 58) = a real memory deficit, not a scale difference. Usable in masked FA as a 2-cohort verbal-memory feature.</t>
-        </is>
-      </c>
-      <c r="J219" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="K219" t="inlineStr">
-        <is>
-          <t>words recalled (0–80)</t>
-        </is>
-      </c>
-      <c r="L219" t="inlineStr">
-        <is>
-          <t>PARTIAL — Comparable in 2 of 3 cohorts (Tier B); usable for 2-cohort joint clustering</t>
-        </is>
-      </c>
-      <c r="M219" t="inlineStr">
-        <is>
-          <t>cvlt_total_recall</t>
-        </is>
-      </c>
-      <c r="N219" t="inlineStr">
-        <is>
-          <t>2 (BP/SZ)</t>
-        </is>
-      </c>
-      <c r="O219" t="inlineStr">
-        <is>
-          <t>Raw count, same code cvlt06_ in BP &amp; SZ; cap [0,80]; robust-z in-pipeline (do NOT use vendor z cvlt06z_ — sparse/outlier-prone in SZ). DR absent (no verbal-list-learning test). Exclude CVLT recognition (cvlt16/cvlt18 — out-of-range/contaminated).</t>
-        </is>
-      </c>
-      <c r="P219" t="inlineStr">
-        <is>
-          <t>Same code &amp; identical 0–80 scale verified in both cohorts; r=0.82 with delayed recall (distinct construct). BP/SZ only — DR has no CVLT.</t>
         </is>
       </c>
     </row>
@@ -16850,34 +16862,29 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>cvlt08_</t>
+          <t>ivt01_w</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>avl01103_</t>
+          <t>ivt01_wais4</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>ivt01</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>CVLT Short-delay free recall</t>
-        </is>
-      </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>Numérique (rappel libre à court terme)</t>
+          <t>WAIS IVT processing-speed index</t>
         </is>
       </c>
       <c r="G220" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H220" t="n">
-        <v>16</v>
-      </c>
-      <c r="I220" t="inlineStr">
-        <is>
-          <t>FEATURE (verbal episodic memory; BP + SZ only — DR has no CVLT). Free recall of the 16-word list after a short delay + interference list — verbal retention across a brief delay. Component of the CVLT verbal-memory domain. Identical 0–16 scale in both cohorts. Near-duplicate of long-delay free recall (r=0.89), so best combined with the other recall indices into a single masked verbal-memory domain rather than entered as an independent feature.</t>
-        </is>
+        <v>160</v>
       </c>
       <c r="J220" t="inlineStr">
         <is>
@@ -16886,32 +16893,27 @@
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>words recalled (0–16)</t>
+          <t>WAIS processing-speed index (mean 100, SD 15)</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>PARTIAL — Comparable in 2 of 3 cohorts (Tier B); usable for 2-cohort joint clustering</t>
+          <t>READY — Comparable in 3 cohorts (Tier A); neuropsy_features.yaml 2026-05-30</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>cvlt_short_delay_free_recall</t>
+          <t>wais_ivt_index</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t>2 (BP/SZ)</t>
+          <t>3 (BP/SZ/DR)</t>
         </is>
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>Raw count; cap [0,16]; BP cvlt08_ ↔ SZ avl01103_ (codes differ, same construct &amp; scale — verified); robust-z in-pipeline. r=0.89 with long-delay → composite into one verbal-memory domain to avoid double-counting. DR absent.</t>
-        </is>
-      </c>
-      <c r="P220" t="inlineStr">
-        <is>
-          <t>BP cvlt08_ ↔ SZ avl01103_; both 0–16 (BP median 12 vs SZ 9); r=0.89 with long-delay (near-duplicate). DR has no CVLT.</t>
+          <t>Index score (100+/-15); present in all 3 cohorts</t>
         </is>
       </c>
     </row>
@@ -16923,33 +16925,33 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>cvlt10_</t>
+          <t>cvlt06_</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>avl01135_</t>
+          <t>cvlt06_</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>CVLT Long-delay free recall (delayed retention)</t>
+          <t>CVLT Total Recall, trials 1–5 (verbal learning / acquisition)</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Numérique (rappel libre à long terme)</t>
+          <t>Numérique (somme des rappels libres, essais 1–5)</t>
         </is>
       </c>
       <c r="G221" t="n">
         <v>0</v>
       </c>
       <c r="H221" t="n">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>FEATURE (verbal episodic memory; BP + SZ only — DR has no CVLT). Free recall of the 16-word list after a ~20-minute delay — delayed retention / consolidation, the standard CVLT "delayed recall" score and clinically dissociable from acquisition (r=0.82 with total recall). Component of the CVLT verbal-memory domain. Identical 0–16 scale in both cohorts; SZ below BP (median 10 vs 13) = real deficit.</t>
+          <t>FEATURE (verbal episodic memory; BP + SZ only — DR has no CVLT). California Verbal Learning Test total free recall summed over the five learning trials — the canonical measure of verbal learning/acquisition. Adds the verbal episodic-memory domain that is otherwise ABSENT from the 3-cohort battery (processing speed, working memory, verbal reasoning, executive shifting — but no memory). Raw count on an identical 16-word/5-trial CVLT in both cohorts (0–80); SZ sits below BP (median 47 vs 58) = a real memory deficit, not a scale difference. Usable in masked FA as a 2-cohort verbal-memory feature.</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -16959,7 +16961,7 @@
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>words recalled (0–16)</t>
+          <t>words recalled (0–80)</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -16969,7 +16971,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>cvlt_long_delay_free_recall</t>
+          <t>cvlt_total_recall</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -16979,12 +16981,12 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>Raw count; cap [0,16]; BP cvlt10_ ↔ SZ avl01135_ (codes differ, same construct &amp; scale — verified); robust-z in-pipeline. DR absent.</t>
+          <t>Raw count, same code cvlt06_ in BP &amp; SZ; cap [0,80]; robust-z in-pipeline (do NOT use vendor z cvlt06z_ — sparse/outlier-prone in SZ). DR absent (no verbal-list-learning test). Exclude CVLT recognition (cvlt16/cvlt18 — out-of-range/contaminated).</t>
         </is>
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>BP cvlt10_ ↔ SZ avl01135_; both 0–16 (BP median 13 vs SZ 10). DR has no CVLT.</t>
+          <t>Same code &amp; identical 0–80 scale verified in both cohorts; r=0.82 with delayed recall (distinct construct). BP/SZ only — DR has no CVLT.</t>
         </is>
       </c>
     </row>
@@ -16996,38 +16998,33 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>fv01_</t>
+          <t>cvlt08_</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>fv01_</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>fv05</t>
+          <t>avl01103_</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Verbal fluency — phonemic (letter): total correct words</t>
+          <t>CVLT Short-delay free recall</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Numérique (nombre de mots corrects en 60 s)</t>
+          <t>Numérique (rappel libre à court terme)</t>
         </is>
       </c>
       <c r="G222" t="n">
         <v>0</v>
       </c>
       <c r="H222" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>FEATURE — phonemic/letter verbal fluency (correct words in 60 s for a given letter). Taps executive function: strategic retrieval, self-monitoring, set-shifting/flexibility; a robust trans-diagnostic cognitive marker present in all 3 cohorts. Raw word count on the same scale (BP/SZ letter "P"; DR "phonologie"); SZ/DR below BP = real cognitive deficit. Complements TMT B−A as an executive/flexibility indicator (dim: Cognitive Flexibility).</t>
+          <t>FEATURE (verbal episodic memory; BP + SZ only — DR has no CVLT). Free recall of the 16-word list after a short delay + interference list — verbal retention across a brief delay. Component of the CVLT verbal-memory domain. Identical 0–16 scale in both cohorts. Near-duplicate of long-delay free recall (r=0.89), so best combined with the other recall indices into a single masked verbal-memory domain rather than entered as an independent feature.</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -17037,32 +17034,32 @@
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>words / 60 s (0–60)</t>
+          <t>words recalled (0–16)</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>READY — Comparable in 3 cohorts (Tier A)</t>
+          <t>PARTIAL — Comparable in 2 of 3 cohorts (Tier B); usable for 2-cohort joint clustering</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>verbal_fluency_phonemic</t>
+          <t>cvlt_short_delay_free_recall</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
         <is>
-          <t>3 (BP/SZ/DR)</t>
+          <t>2 (BP/SZ)</t>
         </is>
       </c>
       <c r="O222" t="inlineStr">
         <is>
-          <t>Raw word count; cap [0,60] (BP has a 229 data-entry outlier); robust-z in-pipeline. COLUMN MAP DIFFERS: BP/SZ `fv01_` but DR=`fv05` (DR `fv01` = "choix du questionnaire", NOT a score). Exclude SZ `FV3_*` (separate computerized TAP flexibility test). Added 2026-06-03 review (not in original neuropsy_features.yaml).</t>
+          <t>Raw count; cap [0,16]; BP cvlt08_ ↔ SZ avl01103_ (codes differ, same construct &amp; scale — verified); robust-z in-pipeline. r=0.89 with long-delay → composite into one verbal-memory domain to avoid double-counting. DR absent.</t>
         </is>
       </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>BP/SZ `fv01_` (letter P) ↔ DR `fv05` (phonologie); raw counts, medians 24/18/20 — same scale verified; SZ&lt;BP real deficit. Coverage 67/42/55%.</t>
+          <t>BP cvlt08_ ↔ SZ avl01103_; both 0–16 (BP median 12 vs SZ 9); r=0.89 with long-delay (near-duplicate). DR has no CVLT.</t>
         </is>
       </c>
     </row>
@@ -17074,38 +17071,33 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>fv12_</t>
+          <t>cvlt10_</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>fv12_</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>fv02</t>
+          <t>avl01135_</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Verbal fluency — semantic (category): total correct words</t>
+          <t>CVLT Long-delay free recall (delayed retention)</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Numérique (nombre de mots corrects en 60 s)</t>
+          <t>Numérique (rappel libre à long terme)</t>
         </is>
       </c>
       <c r="G223" t="n">
         <v>0</v>
       </c>
       <c r="H223" t="n">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>FEATURE — semantic/category verbal fluency (correct words in 60 s for a category). Taps semantic-memory access plus executive search; a standard trans-diagnostic cognitive marker in all 3 cohorts. Raw word count, same scale; SZ/DR below BP = real deficit. Complements phonemic fluency (semantic store vs strategic search) for the Cognitive Flexibility dimension.</t>
+          <t>FEATURE (verbal episodic memory; BP + SZ only — DR has no CVLT). Free recall of the 16-word list after a ~20-minute delay — delayed retention / consolidation, the standard CVLT "delayed recall" score and clinically dissociable from acquisition (r=0.82 with total recall). Component of the CVLT verbal-memory domain. Identical 0–16 scale in both cohorts; SZ below BP (median 10 vs 13) = real deficit.</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -17115,103 +17107,259 @@
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>words / 60 s (0–80)</t>
+          <t>words recalled (0–16)</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>READY — Comparable in 3 cohorts (Tier A)</t>
+          <t>PARTIAL — Comparable in 2 of 3 cohorts (Tier B); usable for 2-cohort joint clustering</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>verbal_fluency_semantic</t>
+          <t>cvlt_long_delay_free_recall</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
         <is>
-          <t>3 (BP/SZ/DR)</t>
+          <t>2 (BP/SZ)</t>
         </is>
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>Raw word count; cap [0,80]; robust-z in-pipeline. COLUMN MAP DIFFERS: BP/SZ `fv12_` but DR=`fv02`. Category: BP/SZ "animaux"; DR "animaux OU fruits" (patient choice — minor comparability caveat). Added 2026-06-03 review.</t>
+          <t>Raw count; cap [0,16]; BP cvlt10_ ↔ SZ avl01135_ (codes differ, same construct &amp; scale — verified); robust-z in-pipeline. DR absent.</t>
         </is>
       </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>BP/SZ `fv12_` (animals) ↔ DR `fv02` (animals or fruits); raw counts, medians 32/24/26 — same scale verified; SZ&lt;BP real deficit. Coverage 67/42/55%.</t>
+          <t>BP cvlt10_ ↔ SZ avl01135_; both 0–16 (BP median 13 vs SZ 10). DR has no CVLT.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>AUTO-QUESTIONNAIRES</t>
+          <t>NEUROPSYCHOLOGIE</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>qidsr113</t>
+          <t>fv01_</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>fv01_</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>qids13</t>
+          <t>fv05</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>QIDS-SR16 item 13 — general interest (anhedonia)</t>
+          <t>Verbal fluency — phonemic (letter): total correct words</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Likert 0–3 (0 = intérêt normal … 3 = perte quasi totale d'intérêt)</t>
+          <t>Numérique (nombre de mots corrects en 60 s)</t>
         </is>
       </c>
       <c r="G224" t="n">
         <v>0</v>
       </c>
       <c r="H224" t="n">
+        <v>60</v>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>FEATURE — phonemic/letter verbal fluency (correct words in 60 s for a given letter). Taps executive function: strategic retrieval, self-monitoring, set-shifting/flexibility; a robust trans-diagnostic cognitive marker present in all 3 cohorts. Raw word count on the same scale (BP/SZ letter "P"; DR "phonologie"); SZ/DR below BP = real cognitive deficit. Complements TMT B−A as an executive/flexibility indicator (dim: Cognitive Flexibility).</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>words / 60 s (0–60)</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>READY — Comparable in 3 cohorts (Tier A)</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>verbal_fluency_phonemic</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>3 (BP/SZ/DR)</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>Raw word count; cap [0,60] (BP has a 229 data-entry outlier); robust-z in-pipeline. COLUMN MAP DIFFERS: BP/SZ `fv01_` but DR=`fv05` (DR `fv01` = "choix du questionnaire", NOT a score). Exclude SZ `FV3_*` (separate computerized TAP flexibility test). Added 2026-06-03 review (not in original neuropsy_features.yaml).</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>BP/SZ `fv01_` (letter P) ↔ DR `fv05` (phonologie); raw counts, medians 24/18/20 — same scale verified; SZ&lt;BP real deficit. Coverage 67/42/55%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>NEUROPSYCHOLOGIE</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>fv12_</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>fv12_</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>fv02</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Verbal fluency — semantic (category): total correct words</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Numérique (nombre de mots corrects en 60 s)</t>
+        </is>
+      </c>
+      <c r="G225" t="n">
+        <v>0</v>
+      </c>
+      <c r="H225" t="n">
+        <v>80</v>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>FEATURE — semantic/category verbal fluency (correct words in 60 s for a category). Taps semantic-memory access plus executive search; a standard trans-diagnostic cognitive marker in all 3 cohorts. Raw word count, same scale; SZ/DR below BP = real deficit. Complements phonemic fluency (semantic store vs strategic search) for the Cognitive Flexibility dimension.</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>words / 60 s (0–80)</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>READY — Comparable in 3 cohorts (Tier A)</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>verbal_fluency_semantic</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>3 (BP/SZ/DR)</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>Raw word count; cap [0,80]; robust-z in-pipeline. COLUMN MAP DIFFERS: BP/SZ `fv12_` but DR=`fv02`. Category: BP/SZ "animaux"; DR "animaux OU fruits" (patient choice — minor comparability caveat). Added 2026-06-03 review.</t>
+        </is>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>BP/SZ `fv12_` (animals) ↔ DR `fv02` (animals or fruits); raw counts, medians 32/24/26 — same scale verified; SZ&lt;BP real deficit. Coverage 67/42/55%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>AUTO-QUESTIONNAIRES</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>qidsr113</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>qids13</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>QIDS-SR16 item 13 — general interest (anhedonia)</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Likert 0–3 (0 = intérêt normal … 3 = perte quasi totale d'intérêt)</t>
+        </is>
+      </c>
+      <c r="G226" t="n">
+        <v>0</v>
+      </c>
+      <c r="H226" t="n">
         <v>3</v>
       </c>
-      <c r="I224" t="inlineStr">
+      <c r="I226" t="inlineStr">
         <is>
           <t>FEATURE (Anhedonia; BP + DR only — SZ has NO QIDS). QIDS-SR16 item 13 ("enthousiasme / intérêt général") is a direct self-report anhedonia indicator (loss of interest). The Anhedonia target dimension is otherwise nearly unmeasured (SHAPS is DR-only). Single item → thin indicator; best composited with other interest/pleasure items into an anhedonia domain. SZ has no anhedonia self-report, so this dimension is 2-cohort (BP/DR).</t>
         </is>
       </c>
-      <c r="J224" t="inlineStr">
+      <c r="J226" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr">
+      <c r="K226" t="inlineStr">
         <is>
           <t>Likert 0–3</t>
         </is>
       </c>
-      <c r="L224" t="inlineStr">
+      <c r="L226" t="inlineStr">
         <is>
           <t>PARTIAL — Comparable in 2 of 3 cohorts (Tier B); usable for 2-cohort joint clustering</t>
         </is>
       </c>
-      <c r="M224" t="inlineStr">
+      <c r="M226" t="inlineStr">
         <is>
           <t>qids_anhedonia_interest</t>
         </is>
       </c>
-      <c r="N224" t="inlineStr">
+      <c r="N226" t="inlineStr">
         <is>
           <t>2 (BP/DR)</t>
         </is>
       </c>
-      <c r="O224" t="inlineStr">
+      <c r="O226" t="inlineStr">
         <is>
           <t>0–3 Likert, identical item in BP `qidsr113` &amp; DR `qids13`; SZ absent (no QIDS). Single-item anhedonia proxy — consider compositing with SHAPS (DR) / MADRS "inability to feel" item for a fuller domain. Do NOT duplicate other QIDS items (sleep→PSQI, suicide→ISF, severity→MADRS).</t>
         </is>
       </c>
-      <c r="P224" t="inlineStr">
+      <c r="P226" t="inlineStr">
         <is>
           <t>BP `qidsr113` == DR `qids13` (identical item, 0–3); ~90% coverage. SZ has no QIDS → no SZ anhedonia measure (dim 4 = Anhedonia is BP/DR only).</t>
         </is>
